--- a/Deliverables/12S/regions/arctic/ADFG_12s_arctic_speciesxsamples.xlsx
+++ b/Deliverables/12S/regions/arctic/ADFG_12s_arctic_speciesxsamples.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN66"/>
+  <dimension ref="A1:AM66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -378,24 +378,24 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Osmerus mordax</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Platichthys stellatus</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Pungitius pungitius</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Myoxocephalus spp.</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Osmerus mordax</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Liparis spp.</t>
@@ -403,57 +403,57 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Clupea pallasii.1</t>
+          <t>Boreogadus saida</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Boreogadus saida</t>
+          <t>Pleuronectes quadrituberculatus</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Pleuronectes quadrituberculatus</t>
+          <t>ASV18</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ASV18</t>
+          <t>ASV20</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ASV20</t>
+          <t>Leptoclinus maculatus</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Leptoclinus maculatus</t>
+          <t>Ammodytes hexapterus</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Ammodytes hexapterus</t>
+          <t>Gadus chalcogrammus</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Gadus chalcogrammus</t>
+          <t>Lepidopsetta spp.</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Lepidopsetta spp.</t>
+          <t>Liparis tunicatus</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Liparis tunicatus</t>
+          <t>Gymnocanthus tricuspis</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Gymnocanthus tricuspis</t>
+          <t>ASV34</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -483,75 +483,70 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>ASV45</t>
+          <t>Hexagrammos spp.</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Hexagrammos lagocephalus</t>
+          <t>Hemilepidotus spp.</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Hemilepidotus spp.</t>
+          <t>ASV52</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>ASV51</t>
+          <t>Stichaeus punctatus</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Stichaeus punctatus</t>
+          <t>Oncorhynchus keta</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Oncorhynchus keta</t>
+          <t>ASV64</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>ASV64</t>
+          <t>ASV70</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>ASV65</t>
+          <t>Nautichthys pribilovius</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Nautichthys pribilovius</t>
+          <t>Pholis clemensi</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Pholis clemensi</t>
+          <t>Podothecus accipenserinus</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Podothecus accipenserinus</t>
+          <t>Gadus spp.</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Gadus spp.</t>
+          <t>ASV141</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>ASV124</t>
+          <t>Sebastolobus spp.</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Sebastolobus spp.</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Cottus aleuticus</t>
         </is>
@@ -569,31 +564,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>16232</v>
+        <v>16233</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>2750</v>
       </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -677,9 +672,6 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
         <v>0</v>
       </c>
     </row>
@@ -716,25 +708,25 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1344</v>
       </c>
       <c r="K3">
-        <v>1346</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="P3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -794,18 +786,15 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK3">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
         <v>0</v>
       </c>
     </row>
@@ -821,7 +810,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>6398</v>
+        <v>6397</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -857,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -929,9 +918,6 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
         <v>0</v>
       </c>
     </row>
@@ -1057,9 +1043,6 @@
       <c r="AM5">
         <v>0</v>
       </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1085,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>4418</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>4419</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1121,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3781</v>
       </c>
       <c r="T6">
-        <v>3829</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -1181,9 +1164,6 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
         <v>0</v>
       </c>
     </row>
@@ -1205,25 +1185,25 @@
         <v>0</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>26</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>726</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
       </c>
       <c r="I7">
         <v>7</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K7">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1241,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R7">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1307,9 +1287,6 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
         <v>0</v>
       </c>
     </row>
@@ -1331,10 +1308,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1349,22 +1326,22 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="L8">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>9364</v>
       </c>
       <c r="N8">
-        <v>9368</v>
+        <v>623</v>
       </c>
       <c r="O8">
-        <v>622</v>
+        <v>318</v>
       </c>
       <c r="P8">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1373,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="T8">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -1433,9 +1410,6 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
         <v>0</v>
       </c>
     </row>
@@ -1463,11 +1437,11 @@
         <v>0</v>
       </c>
       <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>12174</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
       <c r="I9">
         <v>0</v>
       </c>
@@ -1481,16 +1455,16 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>762</v>
       </c>
       <c r="N9">
-        <v>762</v>
+        <v>1349</v>
       </c>
       <c r="O9">
-        <v>1349</v>
+        <v>5702</v>
       </c>
       <c r="P9">
-        <v>5771</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1499,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="T9">
-        <v>350</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>0</v>
@@ -1520,7 +1494,7 @@
         <v>405</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA9">
         <v>0</v>
@@ -1529,10 +1503,10 @@
         <v>0</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="AD9">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
@@ -1559,9 +1533,6 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
         <v>0</v>
       </c>
     </row>
@@ -1577,13 +1548,13 @@
         </is>
       </c>
       <c r="C10">
-        <v>133178</v>
+        <v>132972</v>
       </c>
       <c r="D10">
-        <v>884873</v>
+        <v>886269</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1592,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1607,10 +1578,10 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="N10">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1685,9 +1656,6 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
         <v>0</v>
       </c>
     </row>
@@ -1733,10 +1701,10 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="N11">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1811,9 +1779,6 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
         <v>0</v>
       </c>
     </row>
@@ -1829,13 +1794,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>334646</v>
+        <v>332771</v>
       </c>
       <c r="D12">
-        <v>342986</v>
+        <v>342865</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>140324</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1844,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>140933</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1937,9 +1902,6 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
         <v>0</v>
       </c>
     </row>
@@ -1961,7 +1923,7 @@
         <v>12851</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>3640</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1970,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>3640</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2063,9 +2025,6 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
         <v>0</v>
       </c>
     </row>
@@ -2102,10 +2061,10 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K14">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2189,9 +2148,6 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
         <v>0</v>
       </c>
     </row>
@@ -2210,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>8218</v>
+        <v>8215</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2315,9 +2271,6 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
         <v>0</v>
       </c>
     </row>
@@ -2333,13 +2286,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>8622</v>
+        <v>8623</v>
       </c>
       <c r="D16">
         <v>5842</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>16149</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2348,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>16211</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2441,9 +2394,6 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
         <v>0</v>
       </c>
     </row>
@@ -2531,10 +2481,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2483</v>
       </c>
       <c r="AB17">
-        <v>2483</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -2567,9 +2517,6 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
         <v>0</v>
       </c>
     </row>
@@ -2597,10 +2544,10 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>361</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -2615,13 +2562,13 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="N18">
-        <v>567</v>
+        <v>2042</v>
       </c>
       <c r="O18">
-        <v>2042</v>
+        <v>0</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2651,26 +2598,26 @@
         <v>0</v>
       </c>
       <c r="Y18">
-        <v>4229</v>
+        <v>4230</v>
       </c>
       <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>4</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
         <v>80</v>
       </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>4</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
       <c r="AF18">
         <v>0</v>
       </c>
@@ -2693,9 +2640,6 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>0</v>
-      </c>
-      <c r="AN18">
         <v>0</v>
       </c>
     </row>
@@ -2717,16 +2661,16 @@
         <v>170</v>
       </c>
       <c r="E19">
-        <v>4275</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>4218</v>
       </c>
       <c r="G19">
-        <v>5062</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>5063</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2741,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -2819,9 +2763,6 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
         <v>0</v>
       </c>
     </row>
@@ -2867,16 +2808,16 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1674</v>
       </c>
       <c r="N20">
-        <v>1674</v>
+        <v>53</v>
       </c>
       <c r="O20">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -2945,9 +2886,6 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
         <v>0</v>
       </c>
     </row>
@@ -2975,13 +2913,13 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>8646</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>8616</v>
       </c>
       <c r="I21">
-        <v>4129</v>
+        <v>4133</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3002,16 +2940,16 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="Q21">
-        <v>328</v>
+        <v>1811</v>
       </c>
       <c r="R21">
-        <v>1843</v>
+        <v>626</v>
       </c>
       <c r="S21">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -3053,10 +2991,10 @@
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="AH21">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="AI21">
         <v>0</v>
@@ -3071,9 +3009,6 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
         <v>0</v>
       </c>
     </row>
@@ -3101,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>3163</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>3159</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -3119,16 +3054,16 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>664</v>
       </c>
       <c r="N22">
-        <v>668</v>
+        <v>1365</v>
       </c>
       <c r="O22">
-        <v>1358</v>
+        <v>678</v>
       </c>
       <c r="P22">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3137,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="T22">
-        <v>1155</v>
+        <v>0</v>
       </c>
       <c r="U22">
         <v>0</v>
@@ -3158,23 +3093,23 @@
         <v>0</v>
       </c>
       <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
         <v>121</v>
       </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
       <c r="AF22">
         <v>0</v>
       </c>
@@ -3191,15 +3126,12 @@
         <v>0</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="AL22">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>0</v>
-      </c>
-      <c r="AN22">
         <v>0</v>
       </c>
     </row>
@@ -3215,7 +3147,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>4087</v>
+        <v>4082</v>
       </c>
       <c r="D23">
         <v>13232</v>
@@ -3323,9 +3255,6 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
         <v>0</v>
       </c>
     </row>
@@ -3374,16 +3303,16 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>7</v>
+        <v>7820</v>
       </c>
       <c r="P24">
-        <v>7819</v>
+        <v>1007</v>
       </c>
       <c r="Q24">
-        <v>986</v>
+        <v>0</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -3449,9 +3378,6 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AN24">
         <v>0</v>
       </c>
     </row>
@@ -3467,46 +3393,46 @@
         </is>
       </c>
       <c r="C25">
-        <v>7876</v>
+        <v>7877</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
+        <v>1725</v>
+      </c>
+      <c r="F25">
         <v>35</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>36</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>11</v>
       </c>
-      <c r="H25">
-        <v>1725</v>
-      </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="K25">
-        <v>396</v>
+        <v>321</v>
       </c>
       <c r="L25">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="N25">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="P25">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -3545,16 +3471,16 @@
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="AD25">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF25">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -3575,9 +3501,6 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
         <v>0</v>
       </c>
     </row>
@@ -3596,20 +3519,20 @@
         <v>137</v>
       </c>
       <c r="D26">
-        <v>9221</v>
+        <v>9214</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>267</v>
       </c>
-      <c r="H26">
-        <v>618</v>
-      </c>
       <c r="I26">
         <v>0</v>
       </c>
@@ -3701,9 +3624,6 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
         <v>0</v>
       </c>
     </row>
@@ -3719,7 +3639,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>8160</v>
+        <v>8099</v>
       </c>
       <c r="D27">
         <v>12824</v>
@@ -3731,11 +3651,11 @@
         <v>0</v>
       </c>
       <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>550</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
       <c r="I27">
         <v>0</v>
       </c>
@@ -3749,10 +3669,10 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N27">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -3827,9 +3747,6 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>0</v>
-      </c>
-      <c r="AN27">
         <v>0</v>
       </c>
     </row>
@@ -3851,7 +3768,7 @@
         <v>143</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -3860,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -3953,9 +3870,6 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>0</v>
-      </c>
-      <c r="AN28">
         <v>0</v>
       </c>
     </row>
@@ -3998,10 +3912,10 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -4010,10 +3924,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2669</v>
       </c>
       <c r="Q29">
-        <v>2669</v>
+        <v>0</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -4079,9 +3993,6 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>0</v>
-      </c>
-      <c r="AN29">
         <v>0</v>
       </c>
     </row>
@@ -4109,34 +4020,34 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>1839</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1838</v>
       </c>
       <c r="I30">
         <v>182</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1973</v>
       </c>
       <c r="K30">
-        <v>1974</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="N30">
-        <v>690</v>
+        <v>1729</v>
       </c>
       <c r="O30">
-        <v>1729</v>
+        <v>572</v>
       </c>
       <c r="P30">
-        <v>572</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -4145,13 +4056,13 @@
         <v>0</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1928</v>
       </c>
       <c r="T30">
-        <v>1932</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -4172,10 +4083,10 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="AC30">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -4205,9 +4116,6 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>0</v>
-      </c>
-      <c r="AN30">
         <v>0</v>
       </c>
     </row>
@@ -4235,19 +4143,19 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>6249</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>6343</v>
       </c>
       <c r="I31">
         <v>7</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>38316</v>
       </c>
       <c r="K31">
-        <v>38099</v>
+        <v>0</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4256,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="O31">
-        <v>1845</v>
+        <v>0</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -4271,13 +4179,13 @@
         <v>0</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1385</v>
       </c>
       <c r="T31">
-        <v>1383</v>
+        <v>906</v>
       </c>
       <c r="U31">
-        <v>190</v>
+        <v>49</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -4292,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="Z31">
-        <v>908</v>
+        <v>0</v>
       </c>
       <c r="AA31">
         <v>0</v>
@@ -4301,19 +4209,19 @@
         <v>0</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AD31">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2122</v>
       </c>
       <c r="AG31">
-        <v>2117</v>
+        <v>0</v>
       </c>
       <c r="AH31">
         <v>0</v>
@@ -4331,9 +4239,6 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>0</v>
-      </c>
-      <c r="AN31">
         <v>0</v>
       </c>
     </row>
@@ -4361,19 +4266,19 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>31636</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>32055</v>
       </c>
       <c r="I32">
         <v>155</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>5252</v>
       </c>
       <c r="K32">
-        <v>5250</v>
+        <v>0</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4382,13 +4287,13 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="O32">
-        <v>1150</v>
+        <v>77</v>
       </c>
       <c r="P32">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -4397,13 +4302,13 @@
         <v>0</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>2238</v>
       </c>
       <c r="T32">
-        <v>2237</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -4418,19 +4323,19 @@
         <v>0</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1235</v>
       </c>
       <c r="AD32">
-        <v>1187</v>
+        <v>0</v>
       </c>
       <c r="AE32">
         <v>0</v>
@@ -4454,12 +4359,9 @@
         <v>0</v>
       </c>
       <c r="AL32">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
         <v>0</v>
       </c>
     </row>
@@ -4487,34 +4389,34 @@
         <v>0</v>
       </c>
       <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>21</v>
       </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="N33">
-        <v>646</v>
+        <v>1311</v>
       </c>
       <c r="O33">
-        <v>1311</v>
+        <v>505</v>
       </c>
       <c r="P33">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -4523,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="T33">
-        <v>1499</v>
+        <v>856</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -4544,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="Z33">
-        <v>2293</v>
+        <v>0</v>
       </c>
       <c r="AA33">
         <v>0</v>
@@ -4559,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -4583,9 +4485,6 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>0</v>
-      </c>
-      <c r="AN33">
         <v>0</v>
       </c>
     </row>
@@ -4607,31 +4506,31 @@
         <v>0</v>
       </c>
       <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
         <v>1895</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
       <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>2212</v>
       </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M34">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -4670,16 +4569,16 @@
         <v>0</v>
       </c>
       <c r="Z34">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="AC34">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -4709,9 +4608,6 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>0</v>
-      </c>
-      <c r="AN34">
         <v>0</v>
       </c>
     </row>
@@ -4730,37 +4626,37 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>7963</v>
       </c>
       <c r="E35">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="G35">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="J35">
-        <v>7910</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>6946</v>
       </c>
       <c r="L35">
-        <v>6885</v>
+        <v>37889</v>
       </c>
       <c r="M35">
-        <v>43731</v>
+        <v>487</v>
       </c>
       <c r="N35">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -4769,16 +4665,16 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="R35">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>6808</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -4796,16 +4692,16 @@
         <v>0</v>
       </c>
       <c r="Z35">
-        <v>1511</v>
+        <v>0</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="AC35">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="AD35">
         <v>0</v>
@@ -4826,18 +4722,15 @@
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="AK35">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>0</v>
-      </c>
-      <c r="AN35">
         <v>0</v>
       </c>
     </row>
@@ -4856,37 +4749,37 @@
         <v>21</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="E36">
-        <v>363</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="G36">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>10</v>
+        <v>2358</v>
       </c>
       <c r="N36">
-        <v>2332</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -4895,10 +4788,10 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3597</v>
       </c>
       <c r="R36">
-        <v>3506</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -4961,9 +4854,6 @@
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>0</v>
-      </c>
-      <c r="AN36">
         <v>0</v>
       </c>
     </row>
@@ -5030,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>1475</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -5048,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="Z37">
-        <v>1473</v>
+        <v>0</v>
       </c>
       <c r="AA37">
         <v>0</v>
@@ -5084,12 +4974,9 @@
         <v>0</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="AM37">
-        <v>109</v>
-      </c>
-      <c r="AN37">
         <v>0</v>
       </c>
     </row>
@@ -5108,37 +4995,37 @@
         <v>19</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>38560</v>
       </c>
       <c r="E38">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G38">
-        <v>2316</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>2356</v>
       </c>
       <c r="I38">
-        <v>3861</v>
+        <v>3963</v>
       </c>
       <c r="J38">
-        <v>37052</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>869</v>
       </c>
       <c r="M38">
-        <v>1287</v>
+        <v>377</v>
       </c>
       <c r="N38">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5147,16 +5034,16 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="R38">
-        <v>421</v>
+        <v>2080</v>
       </c>
       <c r="S38">
-        <v>2088</v>
+        <v>288</v>
       </c>
       <c r="T38">
-        <v>288</v>
+        <v>951</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -5174,16 +5061,16 @@
         <v>0</v>
       </c>
       <c r="Z38">
-        <v>971</v>
+        <v>0</v>
       </c>
       <c r="AA38">
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>3018</v>
       </c>
       <c r="AC38">
-        <v>3445</v>
+        <v>0</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5195,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="AH38">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="AI38">
         <v>0</v>
@@ -5213,9 +5100,6 @@
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>0</v>
-      </c>
-      <c r="AN38">
         <v>0</v>
       </c>
     </row>
@@ -5234,55 +5118,55 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>2370</v>
       </c>
       <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
         <v>114</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
       <c r="G39">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I39">
         <v>28</v>
       </c>
       <c r="J39">
-        <v>2362</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="L39">
-        <v>112</v>
+        <v>727</v>
       </c>
       <c r="M39">
-        <v>1108</v>
+        <v>0</v>
       </c>
       <c r="N39">
         <v>0</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="P39">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R39">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="S39">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T39">
-        <v>19</v>
+        <v>421</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -5306,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AC39">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -5321,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AH39">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="AI39">
         <v>0</v>
@@ -5339,9 +5223,6 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>0</v>
-      </c>
-      <c r="AN39">
         <v>0</v>
       </c>
     </row>
@@ -5360,25 +5241,25 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E40">
-        <v>40032</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>40581</v>
       </c>
       <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>41</v>
       </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -5387,10 +5268,10 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>701</v>
       </c>
       <c r="N40">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -5465,9 +5346,6 @@
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>0</v>
-      </c>
-      <c r="AN40">
         <v>0</v>
       </c>
     </row>
@@ -5486,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>3598</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5495,37 +5373,37 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>10642</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>10865</v>
       </c>
       <c r="I41">
-        <v>10466</v>
+        <v>10476</v>
       </c>
       <c r="J41">
-        <v>3541</v>
+        <v>0</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M41">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="N41">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="P41">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Q41">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -5534,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -5552,19 +5430,19 @@
         <v>0</v>
       </c>
       <c r="Z41">
-        <v>6573</v>
+        <v>5591</v>
       </c>
       <c r="AA41">
-        <v>5532</v>
+        <v>0</v>
       </c>
       <c r="AB41">
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="AD41">
-        <v>663</v>
+        <v>0</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -5573,13 +5451,13 @@
         <v>0</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="AH41">
-        <v>359</v>
+        <v>960</v>
       </c>
       <c r="AI41">
-        <v>952</v>
+        <v>0</v>
       </c>
       <c r="AJ41">
         <v>0</v>
@@ -5591,9 +5469,6 @@
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>0</v>
-      </c>
-      <c r="AN41">
         <v>0</v>
       </c>
     </row>
@@ -5612,34 +5487,34 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>5989</v>
       </c>
       <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
         <v>320</v>
       </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
       <c r="G42">
-        <v>23214</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>23473</v>
       </c>
       <c r="I42">
-        <v>3157</v>
+        <v>3215</v>
       </c>
       <c r="J42">
-        <v>5981</v>
+        <v>0</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M42">
-        <v>4252</v>
+        <v>0</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -5648,19 +5523,19 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="Q42">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="R42">
         <v>0</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="T42">
-        <v>142</v>
+        <v>4424</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -5678,16 +5553,16 @@
         <v>0</v>
       </c>
       <c r="Z42">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="AA42">
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2590</v>
       </c>
       <c r="AC42">
-        <v>2589</v>
+        <v>0</v>
       </c>
       <c r="AD42">
         <v>0</v>
@@ -5699,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="AH42">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="AI42">
         <v>0</v>
@@ -5717,9 +5592,6 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>0</v>
-      </c>
-      <c r="AN42">
         <v>0</v>
       </c>
     </row>
@@ -5738,55 +5610,55 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="E43">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="G43">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="I43">
-        <v>2164</v>
+        <v>2168</v>
       </c>
       <c r="J43">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="L43">
-        <v>653</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>4704</v>
       </c>
       <c r="N43">
-        <v>4744</v>
+        <v>8606</v>
       </c>
       <c r="O43">
-        <v>8382</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>868</v>
       </c>
       <c r="Q43">
-        <v>868</v>
+        <v>791</v>
       </c>
       <c r="R43">
-        <v>753</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="T43">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -5819,10 +5691,10 @@
         <v>0</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1561</v>
       </c>
       <c r="AF43">
-        <v>1562</v>
+        <v>0</v>
       </c>
       <c r="AG43">
         <v>0</v>
@@ -5837,15 +5709,12 @@
         <v>0</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL43">
-        <v>198</v>
+        <v>41</v>
       </c>
       <c r="AM43">
-        <v>41</v>
-      </c>
-      <c r="AN43">
         <v>0</v>
       </c>
     </row>
@@ -5867,34 +5736,34 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>9792</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>9795</v>
       </c>
       <c r="G44">
-        <v>1925</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1926</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="K44">
-        <v>83</v>
+        <v>2505</v>
       </c>
       <c r="L44">
-        <v>2506</v>
+        <v>1491</v>
       </c>
       <c r="M44">
-        <v>1532</v>
+        <v>652</v>
       </c>
       <c r="N44">
-        <v>471</v>
+        <v>0</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -5912,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="U44">
         <v>0</v>
@@ -5930,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="Z44">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="AA44">
         <v>0</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>764</v>
       </c>
       <c r="AC44">
-        <v>764</v>
+        <v>0</v>
       </c>
       <c r="AD44">
         <v>0</v>
@@ -5969,9 +5838,6 @@
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>0</v>
-      </c>
-      <c r="AN44">
         <v>0</v>
       </c>
     </row>
@@ -5993,10 +5859,10 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>1314</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1415</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -6005,7 +5871,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>14860</v>
+        <v>15242</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -6017,31 +5883,31 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>16012</v>
       </c>
       <c r="N45">
-        <v>16089</v>
+        <v>0</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>14393</v>
       </c>
       <c r="Q45">
-        <v>14190</v>
+        <v>13252</v>
       </c>
       <c r="R45">
-        <v>13109</v>
+        <v>13601</v>
       </c>
       <c r="S45">
-        <v>13861</v>
+        <v>0</v>
       </c>
       <c r="T45">
         <v>0</v>
       </c>
       <c r="U45">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -6056,7 +5922,7 @@
         <v>0</v>
       </c>
       <c r="Z45">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="AA45">
         <v>0</v>
@@ -6071,10 +5937,10 @@
         <v>0</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="AF45">
-        <v>766</v>
+        <v>0</v>
       </c>
       <c r="AG45">
         <v>0</v>
@@ -6086,18 +5952,15 @@
         <v>0</v>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>557</v>
       </c>
       <c r="AK45">
-        <v>742</v>
+        <v>0</v>
       </c>
       <c r="AL45">
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>0</v>
-      </c>
-      <c r="AN45">
         <v>0</v>
       </c>
     </row>
@@ -6116,55 +5979,55 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>7323</v>
       </c>
       <c r="E46">
-        <v>11391</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>11604</v>
       </c>
       <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
         <v>108</v>
       </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
       <c r="I46">
-        <v>2136</v>
+        <v>2161</v>
       </c>
       <c r="J46">
-        <v>7315</v>
+        <v>72</v>
       </c>
       <c r="K46">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="L46">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="M46">
-        <v>553</v>
+        <v>20614</v>
       </c>
       <c r="N46">
-        <v>20456</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="R46">
-        <v>61</v>
+        <v>2015</v>
       </c>
       <c r="S46">
-        <v>1998</v>
+        <v>523</v>
       </c>
       <c r="T46">
-        <v>513</v>
+        <v>566</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -6182,16 +6045,16 @@
         <v>0</v>
       </c>
       <c r="Z46">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AA46">
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="AC46">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -6206,24 +6069,21 @@
         <v>0</v>
       </c>
       <c r="AH46">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AI46">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="AK46">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="AL46">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AM46">
-        <v>0</v>
-      </c>
-      <c r="AN46">
         <v>0</v>
       </c>
     </row>
@@ -6245,10 +6105,10 @@
         <v>0</v>
       </c>
       <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
         <v>1</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -6269,28 +6129,28 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N47">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="Q47">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="R47">
-        <v>347</v>
+        <v>38</v>
       </c>
       <c r="S47">
-        <v>38</v>
+        <v>156</v>
       </c>
       <c r="T47">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -6311,10 +6171,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="AB47">
-        <v>1029</v>
+        <v>0</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -6347,9 +6207,6 @@
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>0</v>
-      </c>
-      <c r="AN47">
         <v>0</v>
       </c>
     </row>
@@ -6371,17 +6228,17 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
         <v>70</v>
       </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
       <c r="I48">
         <v>0</v>
       </c>
@@ -6389,16 +6246,16 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="L48">
-        <v>578</v>
+        <v>465</v>
       </c>
       <c r="M48">
-        <v>465</v>
+        <v>1355</v>
       </c>
       <c r="N48">
-        <v>1352</v>
+        <v>0</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -6413,10 +6270,10 @@
         <v>0</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="T48">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -6464,18 +6321,15 @@
         <v>0</v>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK48">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL48">
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>0</v>
-      </c>
-      <c r="AN48">
         <v>54</v>
       </c>
     </row>
@@ -6494,55 +6348,55 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="E49">
-        <v>770</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="G49">
-        <v>2797</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>2833</v>
       </c>
       <c r="I49">
-        <v>678</v>
+        <v>832</v>
       </c>
       <c r="J49">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>9087</v>
       </c>
       <c r="L49">
-        <v>9095</v>
+        <v>6386</v>
       </c>
       <c r="M49">
-        <v>7502</v>
+        <v>2251</v>
       </c>
       <c r="N49">
-        <v>2236</v>
+        <v>0</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="Q49">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="R49">
         <v>0</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>3105</v>
       </c>
       <c r="T49">
-        <v>3065</v>
+        <v>1999</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -6560,25 +6414,25 @@
         <v>0</v>
       </c>
       <c r="Z49">
-        <v>1035</v>
+        <v>0</v>
       </c>
       <c r="AA49">
         <v>0</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC49">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD49">
         <v>0</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AF49">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="AG49">
         <v>0</v>
@@ -6599,9 +6453,6 @@
         <v>0</v>
       </c>
       <c r="AM49">
-        <v>0</v>
-      </c>
-      <c r="AN49">
         <v>0</v>
       </c>
     </row>
@@ -6623,10 +6474,10 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>25665</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>25848</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -6641,16 +6492,16 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="L50">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>2587</v>
       </c>
       <c r="N50">
-        <v>2849</v>
+        <v>0</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -6725,9 +6576,6 @@
         <v>0</v>
       </c>
       <c r="AM50">
-        <v>0</v>
-      </c>
-      <c r="AN50">
         <v>0</v>
       </c>
     </row>
@@ -6755,49 +6603,49 @@
         <v>0</v>
       </c>
       <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
         <v>98</v>
       </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1676</v>
       </c>
       <c r="K51">
-        <v>1662</v>
+        <v>81</v>
       </c>
       <c r="L51">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>37</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
         <v>56</v>
       </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>37</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
       <c r="U51">
-        <v>10215</v>
+        <v>10371</v>
       </c>
       <c r="V51">
         <v>0</v>
@@ -6851,9 +6699,6 @@
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>0</v>
-      </c>
-      <c r="AN51">
         <v>0</v>
       </c>
     </row>
@@ -6875,11 +6720,11 @@
         <v>0</v>
       </c>
       <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
         <v>4</v>
       </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
       <c r="G52">
         <v>0</v>
       </c>
@@ -6890,19 +6735,19 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>4859</v>
       </c>
       <c r="K52">
-        <v>4859</v>
+        <v>921</v>
       </c>
       <c r="L52">
-        <v>921</v>
+        <v>54</v>
       </c>
       <c r="M52">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="N52">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -6923,7 +6768,7 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -6977,9 +6822,6 @@
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>0</v>
-      </c>
-      <c r="AN52">
         <v>0</v>
       </c>
     </row>
@@ -6995,7 +6837,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -7004,37 +6846,37 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>1139</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>398</v>
+        <v>1140</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="I53">
         <v>0</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="K53">
-        <v>121</v>
+        <v>38</v>
       </c>
       <c r="L53">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="N53">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="P53">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -7055,7 +6897,7 @@
         <v>0</v>
       </c>
       <c r="W53">
-        <v>6615</v>
+        <v>6672</v>
       </c>
       <c r="X53">
         <v>0</v>
@@ -7076,10 +6918,10 @@
         <v>0</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1378</v>
       </c>
       <c r="AE53">
-        <v>1368</v>
+        <v>0</v>
       </c>
       <c r="AF53">
         <v>0</v>
@@ -7103,9 +6945,6 @@
         <v>0</v>
       </c>
       <c r="AM53">
-        <v>0</v>
-      </c>
-      <c r="AN53">
         <v>0</v>
       </c>
     </row>
@@ -7127,19 +6966,19 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>2321</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>2343</v>
       </c>
       <c r="G54">
-        <v>1851</v>
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>1861</v>
       </c>
       <c r="I54">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -7148,16 +6987,16 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M54">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="N54">
-        <v>74</v>
+        <v>1335</v>
       </c>
       <c r="O54">
-        <v>1310</v>
+        <v>0</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -7169,16 +7008,16 @@
         <v>0</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="T54">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="U54">
         <v>0</v>
       </c>
       <c r="V54">
-        <v>9891</v>
+        <v>10026</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -7190,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="Z54">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AA54">
         <v>0</v>
@@ -7223,15 +7062,12 @@
         <v>0</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="AL54">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="AM54">
-        <v>0</v>
-      </c>
-      <c r="AN54">
         <v>0</v>
       </c>
     </row>
@@ -7253,17 +7089,17 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
         <v>618</v>
       </c>
-      <c r="H55">
-        <v>532</v>
-      </c>
       <c r="I55">
         <v>0</v>
       </c>
@@ -7271,16 +7107,16 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>24044</v>
       </c>
       <c r="L55">
-        <v>23874</v>
+        <v>0</v>
       </c>
       <c r="M55">
-        <v>295</v>
+        <v>6190</v>
       </c>
       <c r="N55">
-        <v>6256</v>
+        <v>0</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -7298,7 +7134,7 @@
         <v>0</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -7355,9 +7191,6 @@
         <v>0</v>
       </c>
       <c r="AM55">
-        <v>0</v>
-      </c>
-      <c r="AN55">
         <v>0</v>
       </c>
     </row>
@@ -7391,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>36012</v>
+        <v>35992</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -7412,13 +7245,13 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2117</v>
       </c>
       <c r="Q56">
-        <v>2117</v>
+        <v>62</v>
       </c>
       <c r="R56">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -7481,9 +7314,6 @@
         <v>0</v>
       </c>
       <c r="AM56">
-        <v>0</v>
-      </c>
-      <c r="AN56">
         <v>0</v>
       </c>
     </row>
@@ -7499,7 +7329,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -7517,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>1339</v>
+        <v>1285</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -7547,10 +7377,10 @@
         <v>0</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="T57">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="U57">
         <v>0</v>
@@ -7607,9 +7437,6 @@
         <v>0</v>
       </c>
       <c r="AM57">
-        <v>0</v>
-      </c>
-      <c r="AN57">
         <v>0</v>
       </c>
     </row>
@@ -7664,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2594</v>
       </c>
       <c r="Q58">
-        <v>2643</v>
+        <v>0</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -7721,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="AI58">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="AJ58">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="AK58">
         <v>0</v>
@@ -7733,9 +7560,6 @@
         <v>0</v>
       </c>
       <c r="AM58">
-        <v>0</v>
-      </c>
-      <c r="AN58">
         <v>0</v>
       </c>
     </row>
@@ -7751,10 +7575,10 @@
         </is>
       </c>
       <c r="C59">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -7769,10 +7593,10 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J59">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -7784,16 +7608,16 @@
         <v>0</v>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O59">
-        <v>26</v>
+        <v>5329</v>
       </c>
       <c r="P59">
-        <v>5328</v>
+        <v>84</v>
       </c>
       <c r="Q59">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -7814,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="X59">
-        <v>9705</v>
+        <v>9789</v>
       </c>
       <c r="Y59">
         <v>0</v>
@@ -7829,10 +7653,10 @@
         <v>0</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>661</v>
       </c>
       <c r="AD59">
-        <v>661</v>
+        <v>0</v>
       </c>
       <c r="AE59">
         <v>0</v>
@@ -7853,15 +7677,12 @@
         <v>0</v>
       </c>
       <c r="AK59">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="AL59">
         <v>0</v>
       </c>
       <c r="AM59">
-        <v>0</v>
-      </c>
-      <c r="AN59">
         <v>0</v>
       </c>
     </row>
@@ -7877,7 +7698,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -7898,25 +7719,25 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>6872</v>
       </c>
       <c r="K60">
-        <v>6743</v>
+        <v>0</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M60">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N60">
         <v>0</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P60">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -7931,7 +7752,7 @@
         <v>0</v>
       </c>
       <c r="U60">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -7985,9 +7806,6 @@
         <v>0</v>
       </c>
       <c r="AM60">
-        <v>0</v>
-      </c>
-      <c r="AN60">
         <v>0</v>
       </c>
     </row>
@@ -8003,40 +7821,40 @@
         </is>
       </c>
       <c r="C61">
-        <v>47972</v>
+        <v>47438</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
         <v>22</v>
       </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
       <c r="G61">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="I61">
         <v>25</v>
       </c>
       <c r="J61">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K61">
-        <v>61</v>
+        <v>409</v>
       </c>
       <c r="L61">
-        <v>406</v>
+        <v>275</v>
       </c>
       <c r="M61">
-        <v>305</v>
+        <v>121</v>
       </c>
       <c r="N61">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -8051,13 +7869,13 @@
         <v>0</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="T61">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="U61">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -8072,7 +7890,7 @@
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="AA61">
         <v>0</v>
@@ -8090,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="AF61">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG61">
         <v>0</v>
@@ -8105,15 +7923,12 @@
         <v>0</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL61">
         <v>0</v>
       </c>
       <c r="AM61">
-        <v>0</v>
-      </c>
-      <c r="AN61">
         <v>0</v>
       </c>
     </row>
@@ -8156,10 +7971,10 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>2548</v>
       </c>
       <c r="M62">
-        <v>2545</v>
+        <v>0</v>
       </c>
       <c r="N62">
         <v>0</v>
@@ -8237,9 +8052,6 @@
         <v>0</v>
       </c>
       <c r="AM62">
-        <v>0</v>
-      </c>
-      <c r="AN62">
         <v>0</v>
       </c>
     </row>
@@ -8255,7 +8067,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>19176</v>
+        <v>19343</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -8279,10 +8091,10 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="L63">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -8309,7 +8121,7 @@
         <v>0</v>
       </c>
       <c r="U63">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="V63">
         <v>0</v>
@@ -8363,9 +8175,6 @@
         <v>0</v>
       </c>
       <c r="AM63">
-        <v>0</v>
-      </c>
-      <c r="AN63">
         <v>0</v>
       </c>
     </row>
@@ -8381,10 +8190,10 @@
         </is>
       </c>
       <c r="C64">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -8393,25 +8202,25 @@
         <v>0</v>
       </c>
       <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
         <v>199</v>
       </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
       <c r="I64">
         <v>0</v>
       </c>
       <c r="J64">
-        <v>4301</v>
+        <v>0</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L64">
-        <v>4</v>
+        <v>1628</v>
       </c>
       <c r="M64">
-        <v>1510</v>
+        <v>0</v>
       </c>
       <c r="N64">
         <v>0</v>
@@ -8456,10 +8265,10 @@
         <v>0</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="AC64">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="AD64">
         <v>0</v>
@@ -8489,9 +8298,6 @@
         <v>0</v>
       </c>
       <c r="AM64">
-        <v>0</v>
-      </c>
-      <c r="AN64">
         <v>0</v>
       </c>
     </row>
@@ -8510,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -8528,19 +8334,19 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>6714</v>
       </c>
       <c r="L65">
-        <v>6713</v>
+        <v>0</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="N65">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -8558,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -8612,12 +8418,9 @@
         <v>0</v>
       </c>
       <c r="AL65">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="AM65">
-        <v>0</v>
-      </c>
-      <c r="AN65">
         <v>0</v>
       </c>
     </row>
@@ -8651,7 +8454,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -8663,10 +8466,10 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N66">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -8738,12 +8541,9 @@
         <v>0</v>
       </c>
       <c r="AL66">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="AM66">
-        <v>134</v>
-      </c>
-      <c r="AN66">
         <v>0</v>
       </c>
     </row>
@@ -8754,7 +8554,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN66"/>
+  <dimension ref="A1:AM66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8780,24 +8580,24 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Osmerus mordax</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Platichthys stellatus</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Pungitius pungitius</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Myoxocephalus spp.</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Osmerus mordax</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Liparis spp.</t>
@@ -8805,57 +8605,57 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Clupea pallasii.1</t>
+          <t>Boreogadus saida</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Boreogadus saida</t>
+          <t>Pleuronectes quadrituberculatus</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Pleuronectes quadrituberculatus</t>
+          <t>ASV18</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ASV18</t>
+          <t>ASV20</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ASV20</t>
+          <t>Leptoclinus maculatus</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Leptoclinus maculatus</t>
+          <t>Ammodytes hexapterus</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Ammodytes hexapterus</t>
+          <t>Gadus chalcogrammus</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Gadus chalcogrammus</t>
+          <t>Lepidopsetta spp.</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Lepidopsetta spp.</t>
+          <t>Liparis tunicatus</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Liparis tunicatus</t>
+          <t>Gymnocanthus tricuspis</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Gymnocanthus tricuspis</t>
+          <t>ASV34</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -8885,75 +8685,70 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>ASV45</t>
+          <t>Hexagrammos spp.</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Hexagrammos lagocephalus</t>
+          <t>Hemilepidotus spp.</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Hemilepidotus spp.</t>
+          <t>ASV52</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>ASV51</t>
+          <t>Stichaeus punctatus</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Stichaeus punctatus</t>
+          <t>Oncorhynchus keta</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Oncorhynchus keta</t>
+          <t>ASV64</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>ASV64</t>
+          <t>ASV70</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>ASV65</t>
+          <t>Nautichthys pribilovius</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Nautichthys pribilovius</t>
+          <t>Pholis clemensi</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Pholis clemensi</t>
+          <t>Podothecus accipenserinus</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Podothecus accipenserinus</t>
+          <t>Gadus spp.</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Gadus spp.</t>
+          <t>ASV141</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>ASV124</t>
+          <t>Sebastolobus spp.</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Sebastolobus spp.</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Cottus aleuticus</t>
         </is>
@@ -8971,31 +8766,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.85355</v>
+        <v>0.85356</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.00026</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.14461</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0.00026</v>
+        <v>0.1446</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.00158</v>
       </c>
       <c r="K2">
-        <v>0.00158</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -9079,9 +8874,6 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
         <v>0</v>
       </c>
     </row>
@@ -9118,25 +8910,25 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.95795</v>
       </c>
       <c r="K3">
-        <v>0.94655</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>0.00214</v>
       </c>
       <c r="N3">
-        <v>0.00211</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.01853</v>
       </c>
       <c r="P3">
-        <v>0.01828</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -9196,18 +8988,15 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>0.02138</v>
       </c>
       <c r="AK3">
-        <v>0.03305</v>
+        <v>0</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
         <v>0</v>
       </c>
     </row>
@@ -9259,10 +9048,10 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.0056</v>
       </c>
       <c r="P4">
-        <v>0.0056</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -9331,9 +9120,6 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
         <v>0</v>
       </c>
     </row>
@@ -9459,9 +9245,6 @@
       <c r="AM5">
         <v>0</v>
       </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9475,7 +9258,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.5238</v>
+        <v>0.52523</v>
       </c>
       <c r="D6">
         <v>0.00144</v>
@@ -9487,10 +9270,10 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.25433</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.25508</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -9523,10 +9306,10 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.21825</v>
       </c>
       <c r="T6">
-        <v>0.22042</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -9583,9 +9366,6 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
         <v>0</v>
       </c>
     </row>
@@ -9607,25 +9387,25 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.03129</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.03136</v>
       </c>
       <c r="G7">
-        <v>0.87365</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.87575</v>
       </c>
       <c r="I7">
-        <v>0.00842</v>
+        <v>0.00844</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.05187</v>
       </c>
       <c r="K7">
-        <v>0.05415</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -9643,10 +9423,10 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>0.03257</v>
       </c>
       <c r="R7">
-        <v>0.03249</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -9709,9 +9489,6 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
         <v>0</v>
       </c>
     </row>
@@ -9733,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.02947</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>0.02957</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -9751,22 +9528,22 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.02019</v>
       </c>
       <c r="L8">
-        <v>0.02019</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>0.83652</v>
       </c>
       <c r="N8">
-        <v>0.83673</v>
+        <v>0.05565</v>
       </c>
       <c r="O8">
-        <v>0.05556</v>
+        <v>0.02841</v>
       </c>
       <c r="P8">
-        <v>0.0284</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -9775,10 +9552,10 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.01036</v>
       </c>
       <c r="T8">
-        <v>0.01036</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -9835,9 +9612,6 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
         <v>0</v>
       </c>
     </row>
@@ -9865,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.5759</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.57787</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -9883,16 +9657,16 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>0.03617</v>
       </c>
       <c r="N9">
-        <v>0.03605</v>
+        <v>0.06403</v>
       </c>
       <c r="O9">
-        <v>0.06382</v>
+        <v>0.27066</v>
       </c>
       <c r="P9">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -9901,10 +9675,10 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>0.01647</v>
       </c>
       <c r="T9">
-        <v>0.01656</v>
+        <v>0.00033</v>
       </c>
       <c r="U9">
         <v>0</v>
@@ -9919,10 +9693,10 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>0.01916</v>
+        <v>0.01922</v>
       </c>
       <c r="Z9">
-        <v>0.00033</v>
+        <v>0</v>
       </c>
       <c r="AA9">
         <v>0</v>
@@ -9931,10 +9705,10 @@
         <v>0</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>0.01524</v>
       </c>
       <c r="AD9">
-        <v>0.01519</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
@@ -9961,9 +9735,6 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
         <v>0</v>
       </c>
     </row>
@@ -9979,13 +9750,13 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.1308</v>
+        <v>0.13045</v>
       </c>
       <c r="D10">
-        <v>0.86909</v>
+        <v>0.86944</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>5E-05</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -9994,7 +9765,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>5E-05</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -10009,10 +9780,10 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>6E-05</v>
       </c>
       <c r="N10">
-        <v>6E-05</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -10087,9 +9858,6 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
         <v>0</v>
       </c>
     </row>
@@ -10135,10 +9903,10 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>0.38614</v>
       </c>
       <c r="N11">
-        <v>0.38614</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -10213,9 +9981,6 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
         <v>0</v>
       </c>
     </row>
@@ -10231,13 +9996,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.40882</v>
+        <v>0.40783</v>
       </c>
       <c r="D12">
-        <v>0.41901</v>
+        <v>0.4202</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.17197</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -10246,7 +10011,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0.17217</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -10339,9 +10104,6 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
         <v>0</v>
       </c>
     </row>
@@ -10363,7 +10125,7 @@
         <v>0.25862</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.07325</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -10372,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0.07325</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -10465,9 +10227,6 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
         <v>0</v>
       </c>
     </row>
@@ -10504,10 +10263,10 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>0.00372</v>
       </c>
       <c r="K14">
-        <v>0.00372</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -10591,9 +10350,6 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
         <v>0</v>
       </c>
     </row>
@@ -10719,9 +10475,6 @@
       <c r="AM15">
         <v>0</v>
       </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10735,13 +10488,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.28108</v>
+        <v>0.28167</v>
       </c>
       <c r="D16">
-        <v>0.19045</v>
+        <v>0.19083</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>0.5275</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -10750,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0.5284799999999999</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -10843,9 +10596,6 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
         <v>0</v>
       </c>
     </row>
@@ -10933,10 +10683,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>0.59559</v>
       </c>
       <c r="AB17">
-        <v>0.59559</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -10969,9 +10719,6 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
         <v>0</v>
       </c>
     </row>
@@ -10987,7 +10734,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.17917</v>
+        <v>0.17945</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -10999,10 +10746,10 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0.04054</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>0.04072</v>
       </c>
       <c r="I18">
         <v>0.00079</v>
@@ -11017,13 +10764,13 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>0.06215</v>
       </c>
       <c r="N18">
-        <v>0.06385</v>
+        <v>0.23032</v>
       </c>
       <c r="O18">
-        <v>0.22995</v>
+        <v>0</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -11053,16 +10800,16 @@
         <v>0</v>
       </c>
       <c r="Y18">
-        <v>0.47624</v>
+        <v>0.4771</v>
       </c>
       <c r="Z18">
-        <v>0.009010000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>0.00045</v>
       </c>
       <c r="AB18">
-        <v>0.00045</v>
+        <v>0</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -11071,7 +10818,7 @@
         <v>0</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>0.00902</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -11095,9 +10842,6 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>0</v>
-      </c>
-      <c r="AN18">
         <v>0</v>
       </c>
     </row>
@@ -11113,22 +10857,22 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.0551</v>
+        <v>0.05526</v>
       </c>
       <c r="D19">
-        <v>0.01688</v>
+        <v>0.01693</v>
       </c>
       <c r="E19">
-        <v>0.4244</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>0.41995</v>
       </c>
       <c r="G19">
-        <v>0.50253</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>0.50408</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -11143,7 +10887,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>0.00269</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -11170,7 +10914,7 @@
         <v>0</v>
       </c>
       <c r="V19">
-        <v>0.00109</v>
+        <v>0.0011</v>
       </c>
       <c r="W19">
         <v>0</v>
@@ -11221,9 +10965,6 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
         <v>0</v>
       </c>
     </row>
@@ -11269,16 +11010,16 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>0.96373</v>
       </c>
       <c r="N20">
-        <v>0.96373</v>
+        <v>0.03051</v>
       </c>
       <c r="O20">
-        <v>0.03051</v>
+        <v>0.00576</v>
       </c>
       <c r="P20">
-        <v>0.00576</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -11347,9 +11088,6 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
         <v>0</v>
       </c>
     </row>
@@ -11377,13 +11115,13 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0.5434</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>0.54349</v>
       </c>
       <c r="I21">
-        <v>0.25951</v>
+        <v>0.26071</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -11404,16 +11142,16 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>0.02069</v>
       </c>
       <c r="Q21">
-        <v>0.02061</v>
+        <v>0.11424</v>
       </c>
       <c r="R21">
-        <v>0.11583</v>
+        <v>0.03949</v>
       </c>
       <c r="S21">
-        <v>0.03934</v>
+        <v>0</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -11455,10 +11193,10 @@
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>0.02138</v>
       </c>
       <c r="AH21">
-        <v>0.02131</v>
+        <v>0</v>
       </c>
       <c r="AI21">
         <v>0</v>
@@ -11473,9 +11211,6 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
         <v>0</v>
       </c>
     </row>
@@ -11491,7 +11226,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.03032</v>
+        <v>0.03035</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -11503,10 +11238,10 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0.40808</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>0.40798</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -11521,16 +11256,16 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>0.08575000000000001</v>
       </c>
       <c r="N22">
-        <v>0.08618000000000001</v>
+        <v>0.17629</v>
       </c>
       <c r="O22">
-        <v>0.1752</v>
+        <v>0.08756</v>
       </c>
       <c r="P22">
-        <v>0.08747000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -11539,10 +11274,10 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>0.14917</v>
       </c>
       <c r="T22">
-        <v>0.14901</v>
+        <v>0</v>
       </c>
       <c r="U22">
         <v>0</v>
@@ -11560,7 +11295,7 @@
         <v>0</v>
       </c>
       <c r="Z22">
-        <v>0.01561</v>
+        <v>0</v>
       </c>
       <c r="AA22">
         <v>0</v>
@@ -11575,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>0.01563</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -11593,15 +11328,12 @@
         <v>0</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>0.04727</v>
       </c>
       <c r="AL22">
-        <v>0.04812</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>0</v>
-      </c>
-      <c r="AN22">
         <v>0</v>
       </c>
     </row>
@@ -11617,10 +11349,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.23598</v>
+        <v>0.23576</v>
       </c>
       <c r="D23">
-        <v>0.76402</v>
+        <v>0.76424</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -11725,9 +11457,6 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
         <v>0</v>
       </c>
     </row>
@@ -11743,7 +11472,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.01299</v>
+        <v>0.01296</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -11776,16 +11505,16 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>0.00078</v>
       </c>
       <c r="O24">
-        <v>0.00078</v>
+        <v>0.87374</v>
       </c>
       <c r="P24">
-        <v>0.87578</v>
+        <v>0.11251</v>
       </c>
       <c r="Q24">
-        <v>0.11044</v>
+        <v>0</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -11851,9 +11580,6 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AN24">
         <v>0</v>
       </c>
     </row>
@@ -11869,46 +11595,46 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.66113</v>
+        <v>0.66115</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
+        <v>0.14479</v>
+      </c>
+      <c r="F25">
         <v>0.00294</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>0.00302</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0.00092</v>
       </c>
-      <c r="H25">
-        <v>0.1448</v>
-      </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>0.03324</v>
       </c>
       <c r="K25">
-        <v>0.03324</v>
+        <v>0.02694</v>
       </c>
       <c r="L25">
-        <v>0.02695</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>0.04289</v>
       </c>
       <c r="N25">
-        <v>0.04289</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>0.00277</v>
       </c>
       <c r="P25">
-        <v>0.00277</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -11947,16 +11673,16 @@
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>0.01066</v>
       </c>
       <c r="AD25">
-        <v>0.01066</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>0.00588</v>
       </c>
       <c r="AF25">
-        <v>0.00588</v>
+        <v>0</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -11977,9 +11703,6 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
         <v>0</v>
       </c>
     </row>
@@ -11995,22 +11718,22 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.01337</v>
+        <v>0.01339</v>
       </c>
       <c r="D26">
-        <v>0.90022</v>
+        <v>0.90024</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>0.06028</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0.02607</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>0.06033</v>
+        <v>0.02609</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -12103,9 +11826,6 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
         <v>0</v>
       </c>
     </row>
@@ -12121,10 +11841,10 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.37694</v>
+        <v>0.37518</v>
       </c>
       <c r="D27">
-        <v>0.59239</v>
+        <v>0.59406</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -12133,10 +11853,10 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0.02541</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>0.02548</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -12151,10 +11871,10 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>0.00528</v>
       </c>
       <c r="N27">
-        <v>0.00527</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -12229,9 +11949,6 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>0</v>
-      </c>
-      <c r="AN27">
         <v>0</v>
       </c>
     </row>
@@ -12253,7 +11970,7 @@
         <v>0.4511</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>0.15773</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -12262,7 +11979,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0.15773</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -12355,9 +12072,6 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>0</v>
-      </c>
-      <c r="AN28">
         <v>0</v>
       </c>
     </row>
@@ -12400,10 +12114,10 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>0.00224</v>
       </c>
       <c r="M29">
-        <v>0.00224</v>
+        <v>0</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -12412,10 +12126,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>0.99776</v>
       </c>
       <c r="Q29">
-        <v>0.99776</v>
+        <v>0</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -12481,9 +12195,6 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>0</v>
-      </c>
-      <c r="AN29">
         <v>0</v>
       </c>
     </row>
@@ -12511,34 +12222,34 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0.1924</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>0.19242</v>
       </c>
       <c r="I30">
-        <v>0.01904</v>
+        <v>0.01905</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>0.20655</v>
       </c>
       <c r="K30">
-        <v>0.20653</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>0.07224</v>
       </c>
       <c r="N30">
-        <v>0.07219</v>
+        <v>0.18101</v>
       </c>
       <c r="O30">
-        <v>0.1809</v>
+        <v>0.05988</v>
       </c>
       <c r="P30">
-        <v>0.05985</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -12547,13 +12258,13 @@
         <v>0</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>0.20184</v>
       </c>
       <c r="T30">
-        <v>0.20213</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>0.03683</v>
+        <v>0.03706</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -12574,10 +12285,10 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>0.02994</v>
       </c>
       <c r="AC30">
-        <v>0.03013</v>
+        <v>0</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -12607,9 +12318,6 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>0</v>
-      </c>
-      <c r="AN30">
         <v>0</v>
       </c>
     </row>
@@ -12637,19 +12345,19 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0.12291</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>0.12429</v>
       </c>
       <c r="I31">
         <v>0.00014</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>0.75081</v>
       </c>
       <c r="K31">
-        <v>0.74938</v>
+        <v>0</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -12658,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>0.03649</v>
       </c>
       <c r="O31">
-        <v>0.03629</v>
+        <v>0</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -12673,13 +12381,13 @@
         <v>0</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>0.02714</v>
       </c>
       <c r="T31">
-        <v>0.0272</v>
+        <v>0.01775</v>
       </c>
       <c r="U31">
-        <v>0.00374</v>
+        <v>0.00096</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -12694,7 +12402,7 @@
         <v>0</v>
       </c>
       <c r="Z31">
-        <v>0.01786</v>
+        <v>0</v>
       </c>
       <c r="AA31">
         <v>0</v>
@@ -12703,19 +12411,19 @@
         <v>0</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>0.00084</v>
       </c>
       <c r="AD31">
-        <v>0.00085</v>
+        <v>0</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>0.04158</v>
       </c>
       <c r="AG31">
-        <v>0.04164</v>
+        <v>0</v>
       </c>
       <c r="AH31">
         <v>0</v>
@@ -12733,9 +12441,6 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>0</v>
-      </c>
-      <c r="AN31">
         <v>0</v>
       </c>
     </row>
@@ -12763,19 +12468,19 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0.7567700000000001</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>0.75637</v>
       </c>
       <c r="I32">
-        <v>0.00371</v>
+        <v>0.00366</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>0.12393</v>
       </c>
       <c r="K32">
-        <v>0.12559</v>
+        <v>0</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -12784,13 +12489,13 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>0.02714</v>
       </c>
       <c r="O32">
-        <v>0.02751</v>
+        <v>0.00182</v>
       </c>
       <c r="P32">
-        <v>0.00184</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -12799,13 +12504,13 @@
         <v>0</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>0.05281</v>
       </c>
       <c r="T32">
-        <v>0.05351</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>0.00167</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -12820,19 +12525,19 @@
         <v>0</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>0.00399</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>0.00116</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>0.02914</v>
       </c>
       <c r="AD32">
-        <v>0.02839</v>
+        <v>0</v>
       </c>
       <c r="AE32">
         <v>0</v>
@@ -12856,12 +12561,9 @@
         <v>0</v>
       </c>
       <c r="AL32">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
         <v>0</v>
       </c>
     </row>
@@ -12889,34 +12591,34 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>0.00334</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>0.00333</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>0.00063</v>
       </c>
       <c r="K33">
-        <v>0.0006400000000000001</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>0.10244</v>
       </c>
       <c r="N33">
-        <v>0.10288</v>
+        <v>0.2079</v>
       </c>
       <c r="O33">
-        <v>0.20879</v>
+        <v>0.08008</v>
       </c>
       <c r="P33">
-        <v>0.08043</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -12925,10 +12627,10 @@
         <v>0</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>0.23771</v>
       </c>
       <c r="T33">
-        <v>0.23873</v>
+        <v>0.13574</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -12946,7 +12648,7 @@
         <v>0</v>
       </c>
       <c r="Z33">
-        <v>0.36519</v>
+        <v>0</v>
       </c>
       <c r="AA33">
         <v>0</v>
@@ -12961,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>0.23216</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -12985,9 +12687,6 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>0</v>
-      </c>
-      <c r="AN33">
         <v>0</v>
       </c>
     </row>
@@ -13009,31 +12708,31 @@
         <v>0</v>
       </c>
       <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
         <v>0.43147</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
       <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>0.50364</v>
       </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>0.00046</v>
       </c>
       <c r="K34">
-        <v>0.00046</v>
+        <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>0.00319</v>
       </c>
       <c r="M34">
-        <v>0.00319</v>
+        <v>0</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -13072,16 +12771,16 @@
         <v>0</v>
       </c>
       <c r="Z34">
-        <v>0.04463</v>
+        <v>0</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>0.06125</v>
       </c>
       <c r="AC34">
-        <v>0.01662</v>
+        <v>0</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -13111,9 +12810,6 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>0</v>
-      </c>
-      <c r="AN34">
         <v>0</v>
       </c>
     </row>
@@ -13132,37 +12828,37 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>0.12935</v>
       </c>
       <c r="E35">
-        <v>0.00214</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>0.00213</v>
       </c>
       <c r="G35">
-        <v>0.00712</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>0.00721</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>0.00455</v>
       </c>
       <c r="J35">
-        <v>0.12821</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>0.11283</v>
       </c>
       <c r="L35">
-        <v>0.1116</v>
+        <v>0.61548</v>
       </c>
       <c r="M35">
-        <v>0.7088100000000001</v>
+        <v>0.00791</v>
       </c>
       <c r="N35">
-        <v>0.007860000000000001</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -13171,16 +12867,16 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>0.00201</v>
       </c>
       <c r="R35">
-        <v>0.00198</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>0.11059</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -13198,16 +12894,16 @@
         <v>0</v>
       </c>
       <c r="Z35">
-        <v>0.02449</v>
+        <v>0</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>0.00481</v>
       </c>
       <c r="AC35">
-        <v>0.00478</v>
+        <v>0</v>
       </c>
       <c r="AD35">
         <v>0</v>
@@ -13228,18 +12924,15 @@
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>0.00312</v>
       </c>
       <c r="AK35">
-        <v>0.00301</v>
+        <v>0</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>0</v>
-      </c>
-      <c r="AN35">
         <v>0</v>
       </c>
     </row>
@@ -13255,40 +12948,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.00324</v>
+        <v>0.00317</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>0.01857</v>
       </c>
       <c r="E36">
-        <v>0.05593</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>0.05723</v>
       </c>
       <c r="G36">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>0.02024</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0.01895</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>0.00151</v>
       </c>
       <c r="M36">
-        <v>0.00154</v>
+        <v>0.35609</v>
       </c>
       <c r="N36">
-        <v>0.35932</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -13297,10 +12990,10 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>0.54319</v>
       </c>
       <c r="R36">
-        <v>0.54022</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -13363,9 +13056,6 @@
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>0</v>
-      </c>
-      <c r="AN36">
         <v>0</v>
       </c>
     </row>
@@ -13432,7 +13122,7 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>0.93119</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -13450,7 +13140,7 @@
         <v>0</v>
       </c>
       <c r="Z37">
-        <v>0.9311</v>
+        <v>0</v>
       </c>
       <c r="AA37">
         <v>0</v>
@@ -13486,12 +13176,9 @@
         <v>0</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>0.06881</v>
       </c>
       <c r="AM37">
-        <v>0.0689</v>
-      </c>
-      <c r="AN37">
         <v>0</v>
       </c>
     </row>
@@ -13510,55 +13197,55 @@
         <v>0.00036</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>0.72558</v>
       </c>
       <c r="E38">
-        <v>0.00027</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>0.00032</v>
       </c>
       <c r="G38">
-        <v>0.0442</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>0.04433</v>
       </c>
       <c r="I38">
-        <v>0.07368</v>
+        <v>0.07457</v>
       </c>
       <c r="J38">
-        <v>0.70707</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>0.01635</v>
       </c>
       <c r="M38">
-        <v>0.02456</v>
+        <v>0.00709</v>
       </c>
       <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
         <v>0.00792</v>
       </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
       <c r="R38">
-        <v>0.008030000000000001</v>
+        <v>0.03914</v>
       </c>
       <c r="S38">
-        <v>0.03985</v>
+        <v>0.00542</v>
       </c>
       <c r="T38">
-        <v>0.0055</v>
+        <v>0.01789</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -13576,16 +13263,16 @@
         <v>0</v>
       </c>
       <c r="Z38">
-        <v>0.01853</v>
+        <v>0</v>
       </c>
       <c r="AA38">
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>0.05679</v>
       </c>
       <c r="AC38">
-        <v>0.06574000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -13597,10 +13284,10 @@
         <v>0</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>0.00423</v>
       </c>
       <c r="AH38">
-        <v>0.00429</v>
+        <v>0</v>
       </c>
       <c r="AI38">
         <v>0</v>
@@ -13615,9 +13302,6 @@
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>0</v>
-      </c>
-      <c r="AN38">
         <v>0</v>
       </c>
     </row>
@@ -13636,55 +13320,55 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>0.55116</v>
       </c>
       <c r="E39">
-        <v>0.0265</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>0.02651</v>
       </c>
       <c r="G39">
-        <v>0.01976</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>0.01209</v>
       </c>
       <c r="I39">
         <v>0.00651</v>
       </c>
       <c r="J39">
-        <v>0.54905</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>0.02605</v>
       </c>
       <c r="L39">
-        <v>0.02603</v>
+        <v>0.16907</v>
       </c>
       <c r="M39">
-        <v>0.25755</v>
+        <v>0</v>
       </c>
       <c r="N39">
         <v>0</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P39">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>0.02279</v>
       </c>
       <c r="R39">
-        <v>0.02278</v>
+        <v>0.00465</v>
       </c>
       <c r="S39">
-        <v>0.00465</v>
+        <v>0.00442</v>
       </c>
       <c r="T39">
-        <v>0.00442</v>
+        <v>0.09791</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -13708,10 +13392,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>0.02651</v>
       </c>
       <c r="AC39">
-        <v>0.03045</v>
+        <v>0</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -13723,10 +13407,10 @@
         <v>0</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>0.04233</v>
       </c>
       <c r="AH39">
-        <v>0.04231</v>
+        <v>0</v>
       </c>
       <c r="AI39">
         <v>0</v>
@@ -13741,9 +13425,6 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>0</v>
-      </c>
-      <c r="AN39">
         <v>0</v>
       </c>
     </row>
@@ -13762,25 +13443,25 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>0.00155</v>
       </c>
       <c r="E40">
-        <v>0.97687</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>0.98053</v>
       </c>
       <c r="G40">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>0.00099</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0.00156</v>
+        <v>0</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -13789,10 +13470,10 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>0.01694</v>
       </c>
       <c r="N40">
-        <v>0.02057</v>
+        <v>0</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -13867,9 +13548,6 @@
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>0</v>
-      </c>
-      <c r="AN40">
         <v>0</v>
       </c>
     </row>
@@ -13888,7 +13566,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>0.09153</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -13897,37 +13575,37 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0.27369</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>0.27639</v>
       </c>
       <c r="I41">
-        <v>0.26916</v>
+        <v>0.2665</v>
       </c>
       <c r="J41">
-        <v>0.09107</v>
+        <v>0</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>0.00074</v>
       </c>
       <c r="M41">
-        <v>0.00077</v>
+        <v>0.00221</v>
       </c>
       <c r="N41">
-        <v>0.00219</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>0.00066</v>
       </c>
       <c r="P41">
-        <v>0.00067</v>
+        <v>0.00038</v>
       </c>
       <c r="Q41">
-        <v>0.00039</v>
+        <v>0</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -13936,7 +13614,7 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>0.1679</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -13954,19 +13632,19 @@
         <v>0</v>
       </c>
       <c r="Z41">
-        <v>0.16904</v>
+        <v>0.14223</v>
       </c>
       <c r="AA41">
-        <v>0.14227</v>
+        <v>0</v>
       </c>
       <c r="AB41">
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>0.01778</v>
       </c>
       <c r="AD41">
-        <v>0.01705</v>
+        <v>0</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -13975,13 +13653,13 @@
         <v>0</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>0.009259999999999999</v>
       </c>
       <c r="AH41">
-        <v>0.00923</v>
+        <v>0.02442</v>
       </c>
       <c r="AI41">
-        <v>0.02448</v>
+        <v>0</v>
       </c>
       <c r="AJ41">
         <v>0</v>
@@ -13993,9 +13671,6 @@
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>0</v>
-      </c>
-      <c r="AN41">
         <v>0</v>
       </c>
     </row>
@@ -14014,34 +13689,34 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>0.14818</v>
       </c>
       <c r="E42">
-        <v>0.007979999999999999</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>0.00792</v>
       </c>
       <c r="G42">
-        <v>0.5791500000000001</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>0.5807600000000001</v>
       </c>
       <c r="I42">
-        <v>0.07876</v>
+        <v>0.07954</v>
       </c>
       <c r="J42">
-        <v>0.14922</v>
+        <v>0</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>0.00114</v>
       </c>
       <c r="M42">
-        <v>0.10608</v>
+        <v>0</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -14050,19 +13725,19 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>0.0023</v>
       </c>
       <c r="Q42">
-        <v>0.00232</v>
+        <v>0</v>
       </c>
       <c r="R42">
         <v>0</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>0.00359</v>
       </c>
       <c r="T42">
-        <v>0.00354</v>
+        <v>0.10946</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -14080,16 +13755,16 @@
         <v>0</v>
       </c>
       <c r="Z42">
-        <v>0.00524</v>
+        <v>0</v>
       </c>
       <c r="AA42">
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>0.06408</v>
       </c>
       <c r="AC42">
-        <v>0.06458999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD42">
         <v>0</v>
@@ -14101,10 +13776,10 @@
         <v>0</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>0.00304</v>
       </c>
       <c r="AH42">
-        <v>0.00312</v>
+        <v>0</v>
       </c>
       <c r="AI42">
         <v>0</v>
@@ -14119,9 +13794,6 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>0</v>
-      </c>
-      <c r="AN42">
         <v>0</v>
       </c>
     </row>
@@ -14140,55 +13812,55 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>0.01192</v>
       </c>
       <c r="E43">
-        <v>0.02752</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>0.02769</v>
       </c>
       <c r="G43">
-        <v>0.00661</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>0.00654</v>
       </c>
       <c r="I43">
-        <v>0.10598</v>
+        <v>0.10587</v>
       </c>
       <c r="J43">
-        <v>0.01195</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>0.03189</v>
       </c>
       <c r="L43">
-        <v>0.03198</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>0.22971</v>
       </c>
       <c r="N43">
-        <v>0.23234</v>
+        <v>0.42026</v>
       </c>
       <c r="O43">
-        <v>0.41052</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>0.04239</v>
       </c>
       <c r="Q43">
-        <v>0.04251</v>
+        <v>0.03863</v>
       </c>
       <c r="R43">
-        <v>0.03688</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>0.00542</v>
       </c>
       <c r="T43">
-        <v>0.00549</v>
+        <v>0.0001</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -14221,10 +13893,10 @@
         <v>0</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>0.07623000000000001</v>
       </c>
       <c r="AF43">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
       <c r="AG43">
         <v>0</v>
@@ -14239,15 +13911,12 @@
         <v>0</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>0.00137</v>
       </c>
       <c r="AL43">
-        <v>0.0097</v>
+        <v>0.002</v>
       </c>
       <c r="AM43">
-        <v>0.00201</v>
-      </c>
-      <c r="AN43">
         <v>0</v>
       </c>
     </row>
@@ -14269,34 +13938,34 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0.55996</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>0.5555600000000001</v>
       </c>
       <c r="G44">
-        <v>0.11008</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>0.10924</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>0.00471</v>
       </c>
       <c r="K44">
-        <v>0.00475</v>
+        <v>0.14208</v>
       </c>
       <c r="L44">
-        <v>0.14331</v>
+        <v>0.08457000000000001</v>
       </c>
       <c r="M44">
-        <v>0.08760999999999999</v>
+        <v>0.03698</v>
       </c>
       <c r="N44">
-        <v>0.02693</v>
+        <v>0</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -14314,7 +13983,7 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>0.02354</v>
       </c>
       <c r="U44">
         <v>0</v>
@@ -14332,16 +14001,16 @@
         <v>0</v>
       </c>
       <c r="Z44">
-        <v>0.02367</v>
+        <v>0</v>
       </c>
       <c r="AA44">
         <v>0</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>0.04333</v>
       </c>
       <c r="AC44">
-        <v>0.04369</v>
+        <v>0</v>
       </c>
       <c r="AD44">
         <v>0</v>
@@ -14371,9 +14040,6 @@
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>0</v>
-      </c>
-      <c r="AN44">
         <v>0</v>
       </c>
     </row>
@@ -14395,10 +14061,10 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0.01741</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>0.01869</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -14407,7 +14073,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>0.19692</v>
+        <v>0.2013</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -14419,31 +14085,31 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>0.21147</v>
       </c>
       <c r="N45">
-        <v>0.2132</v>
+        <v>0</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>0.19009</v>
       </c>
       <c r="Q45">
-        <v>0.18804</v>
+        <v>0.17502</v>
       </c>
       <c r="R45">
-        <v>0.17371</v>
+        <v>0.17963</v>
       </c>
       <c r="S45">
-        <v>0.18368</v>
+        <v>0</v>
       </c>
       <c r="T45">
         <v>0</v>
       </c>
       <c r="U45">
-        <v>0.00083</v>
+        <v>0</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -14458,7 +14124,7 @@
         <v>0</v>
       </c>
       <c r="Z45">
-        <v>0.00623</v>
+        <v>0</v>
       </c>
       <c r="AA45">
         <v>0</v>
@@ -14473,10 +14139,10 @@
         <v>0</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>0.01646</v>
       </c>
       <c r="AF45">
-        <v>0.01015</v>
+        <v>0</v>
       </c>
       <c r="AG45">
         <v>0</v>
@@ -14488,18 +14154,15 @@
         <v>0</v>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>0.00736</v>
       </c>
       <c r="AK45">
-        <v>0.00983</v>
+        <v>0</v>
       </c>
       <c r="AL45">
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>0</v>
-      </c>
-      <c r="AN45">
         <v>0</v>
       </c>
     </row>
@@ -14518,55 +14181,55 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>0.15864</v>
       </c>
       <c r="E46">
-        <v>0.24904</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>0.25139</v>
       </c>
       <c r="G46">
-        <v>0.00236</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>0.00234</v>
       </c>
       <c r="I46">
-        <v>0.0467</v>
+        <v>0.04682</v>
       </c>
       <c r="J46">
-        <v>0.15993</v>
+        <v>0.00156</v>
       </c>
       <c r="K46">
-        <v>0.00157</v>
+        <v>0.00292</v>
       </c>
       <c r="L46">
-        <v>0.00295</v>
+        <v>0.00431</v>
       </c>
       <c r="M46">
-        <v>0.01209</v>
+        <v>0.44658</v>
       </c>
       <c r="N46">
-        <v>0.44723</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>0.00052</v>
+        <v>0</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>0.00132</v>
       </c>
       <c r="R46">
-        <v>0.00133</v>
+        <v>0.04365</v>
       </c>
       <c r="S46">
-        <v>0.04368</v>
+        <v>0.01133</v>
       </c>
       <c r="T46">
-        <v>0.01122</v>
+        <v>0.01226</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -14584,16 +14247,16 @@
         <v>0</v>
       </c>
       <c r="Z46">
-        <v>0.00232</v>
+        <v>0</v>
       </c>
       <c r="AA46">
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>0.00745</v>
       </c>
       <c r="AC46">
-        <v>0.00899</v>
+        <v>0</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -14608,24 +14271,21 @@
         <v>0</v>
       </c>
       <c r="AH46">
-        <v>0</v>
+        <v>0.00154</v>
       </c>
       <c r="AI46">
-        <v>0.00155</v>
+        <v>0</v>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>0.007889999999999999</v>
       </c>
       <c r="AK46">
-        <v>0.00791</v>
+        <v>0</v>
       </c>
       <c r="AL46">
-        <v>0.00059</v>
+        <v>0</v>
       </c>
       <c r="AM46">
-        <v>0</v>
-      </c>
-      <c r="AN46">
         <v>0</v>
       </c>
     </row>
@@ -14647,11 +14307,11 @@
         <v>0</v>
       </c>
       <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
         <v>0.00046</v>
       </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
       <c r="G47">
         <v>0</v>
       </c>
@@ -14659,7 +14319,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0.15799</v>
+        <v>0.15785</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -14671,28 +14331,28 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>0.08283</v>
       </c>
       <c r="N47">
-        <v>0.08291</v>
+        <v>0</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>0.0359</v>
       </c>
       <c r="Q47">
-        <v>0.03593</v>
+        <v>0.16015</v>
       </c>
       <c r="R47">
-        <v>0.15983</v>
+        <v>0.01749</v>
       </c>
       <c r="S47">
-        <v>0.0175</v>
+        <v>0.07179000000000001</v>
       </c>
       <c r="T47">
-        <v>0.07140000000000001</v>
+        <v>0</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -14713,10 +14373,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>0.47354</v>
       </c>
       <c r="AB47">
-        <v>0.47398</v>
+        <v>0</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -14749,9 +14409,6 @@
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>0</v>
-      </c>
-      <c r="AN47">
         <v>0</v>
       </c>
     </row>
@@ -14773,16 +14430,16 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0.03783</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>0.03811</v>
       </c>
       <c r="G48">
-        <v>0.02283</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>0.0228</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -14791,16 +14448,16 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>0.18827</v>
       </c>
       <c r="L48">
-        <v>0.18852</v>
+        <v>0.15147</v>
       </c>
       <c r="M48">
-        <v>0.15166</v>
+        <v>0.44137</v>
       </c>
       <c r="N48">
-        <v>0.44097</v>
+        <v>0</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -14815,10 +14472,10 @@
         <v>0</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>0.10782</v>
       </c>
       <c r="T48">
-        <v>0.10796</v>
+        <v>0</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -14866,19 +14523,16 @@
         <v>0</v>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>0.03257</v>
       </c>
       <c r="AK48">
-        <v>0.03262</v>
+        <v>0</v>
       </c>
       <c r="AL48">
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>0</v>
-      </c>
-      <c r="AN48">
-        <v>0.01761</v>
+        <v>0.01759</v>
       </c>
     </row>
     <row r="49">
@@ -14896,55 +14550,55 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>0.0077</v>
       </c>
       <c r="E49">
-        <v>0.02795</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>0.02789</v>
       </c>
       <c r="G49">
-        <v>0.10153</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>0.10246</v>
       </c>
       <c r="I49">
-        <v>0.02461</v>
+        <v>0.03009</v>
       </c>
       <c r="J49">
-        <v>0.00766</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>0.32866</v>
       </c>
       <c r="L49">
-        <v>0.33014</v>
+        <v>0.23097</v>
       </c>
       <c r="M49">
-        <v>0.27231</v>
+        <v>0.08141</v>
       </c>
       <c r="N49">
-        <v>0.08116</v>
+        <v>0</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>0.00369</v>
       </c>
       <c r="Q49">
-        <v>0.00367</v>
+        <v>0</v>
       </c>
       <c r="R49">
         <v>0</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>0.1123</v>
       </c>
       <c r="T49">
-        <v>0.11126</v>
+        <v>0.0723</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -14962,25 +14616,25 @@
         <v>0</v>
       </c>
       <c r="Z49">
-        <v>0.03757</v>
+        <v>0</v>
       </c>
       <c r="AA49">
         <v>0</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>0.00083</v>
       </c>
       <c r="AC49">
-        <v>0.00044</v>
+        <v>0</v>
       </c>
       <c r="AD49">
         <v>0</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="AF49">
-        <v>0.00171</v>
+        <v>0</v>
       </c>
       <c r="AG49">
         <v>0</v>
@@ -15001,9 +14655,6 @@
         <v>0</v>
       </c>
       <c r="AM49">
-        <v>0</v>
-      </c>
-      <c r="AN49">
         <v>0</v>
       </c>
     </row>
@@ -15025,10 +14676,10 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0.89152</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>0.90038</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -15043,16 +14694,16 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>0.009509999999999999</v>
       </c>
       <c r="L50">
-        <v>0.009520000000000001</v>
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>0.09011</v>
       </c>
       <c r="N50">
-        <v>0.09896000000000001</v>
+        <v>0</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -15127,9 +14778,6 @@
         <v>0</v>
       </c>
       <c r="AM50">
-        <v>0</v>
-      </c>
-      <c r="AN50">
         <v>0</v>
       </c>
     </row>
@@ -15157,31 +14805,31 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0.008070000000000001</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>0.00796</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>0.13605</v>
       </c>
       <c r="K51">
-        <v>0.1368</v>
+        <v>0.00658</v>
       </c>
       <c r="L51">
-        <v>0.00667</v>
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>0.00461</v>
+        <v>0</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="O51">
-        <v>0.00305</v>
+        <v>0</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -15196,10 +14844,10 @@
         <v>0</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>0.00455</v>
       </c>
       <c r="U51">
-        <v>0.8408099999999999</v>
+        <v>0.84187</v>
       </c>
       <c r="V51">
         <v>0</v>
@@ -15253,9 +14901,6 @@
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>0</v>
-      </c>
-      <c r="AN51">
         <v>0</v>
       </c>
     </row>
@@ -15277,11 +14922,11 @@
         <v>0</v>
       </c>
       <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
         <v>0.00065</v>
       </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
       <c r="G52">
         <v>0</v>
       </c>
@@ -15292,19 +14937,19 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>0.78944</v>
       </c>
       <c r="K52">
-        <v>0.78982</v>
+        <v>0.14963</v>
       </c>
       <c r="L52">
-        <v>0.14971</v>
+        <v>0.00877</v>
       </c>
       <c r="M52">
-        <v>0.00878</v>
+        <v>0.03038</v>
       </c>
       <c r="N52">
-        <v>0.0304</v>
+        <v>0</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -15325,7 +14970,7 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>0.02064</v>
+        <v>0.02112</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -15379,9 +15024,6 @@
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>0</v>
-      </c>
-      <c r="AN52">
         <v>0</v>
       </c>
     </row>
@@ -15397,7 +15039,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>0.06322999999999999</v>
+        <v>0.0629</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -15406,37 +15048,37 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>0.10749</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>0.03756</v>
+        <v>0.10687</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>0.03759</v>
       </c>
       <c r="I53">
         <v>0</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>0.01134</v>
       </c>
       <c r="K53">
-        <v>0.01142</v>
+        <v>0.00356</v>
       </c>
       <c r="L53">
-        <v>0.00359</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>0.00487</v>
       </c>
       <c r="N53">
-        <v>0.00491</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>0.01819</v>
       </c>
       <c r="P53">
-        <v>0.0184</v>
+        <v>0</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -15457,7 +15099,7 @@
         <v>0</v>
       </c>
       <c r="W53">
-        <v>0.62429</v>
+        <v>0.62548</v>
       </c>
       <c r="X53">
         <v>0</v>
@@ -15478,10 +15120,10 @@
         <v>0</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>0.12918</v>
       </c>
       <c r="AE53">
-        <v>0.12911</v>
+        <v>0</v>
       </c>
       <c r="AF53">
         <v>0</v>
@@ -15505,9 +15147,6 @@
         <v>0</v>
       </c>
       <c r="AM53">
-        <v>0</v>
-      </c>
-      <c r="AN53">
         <v>0</v>
       </c>
     </row>
@@ -15523,25 +15162,25 @@
         </is>
       </c>
       <c r="C54">
-        <v>0.11346</v>
+        <v>0.1127</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0.12759</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>0.12793</v>
       </c>
       <c r="G54">
-        <v>0.10175</v>
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>0.10162</v>
       </c>
       <c r="I54">
-        <v>0.00726</v>
+        <v>0.0083</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -15550,16 +15189,16 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>0.00475</v>
       </c>
       <c r="M54">
-        <v>0.00473</v>
+        <v>0.0042</v>
       </c>
       <c r="N54">
-        <v>0.00407</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="O54">
-        <v>0.07201</v>
+        <v>0</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -15571,16 +15210,16 @@
         <v>0</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>0.00519</v>
       </c>
       <c r="T54">
-        <v>0.00522</v>
+        <v>0.00415</v>
       </c>
       <c r="U54">
         <v>0</v>
       </c>
       <c r="V54">
-        <v>0.54373</v>
+        <v>0.54745</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -15592,7 +15231,7 @@
         <v>0</v>
       </c>
       <c r="Z54">
-        <v>0.00412</v>
+        <v>0</v>
       </c>
       <c r="AA54">
         <v>0</v>
@@ -15625,15 +15264,12 @@
         <v>0</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>0.01081</v>
       </c>
       <c r="AL54">
-        <v>0.01605</v>
+        <v>0</v>
       </c>
       <c r="AM54">
-        <v>0</v>
-      </c>
-      <c r="AN54">
         <v>0</v>
       </c>
     </row>
@@ -15649,22 +15285,22 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.02084</v>
+        <v>0.02077</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>0.01641</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0.01916</v>
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>0.0165</v>
+        <v>0.0191</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -15673,16 +15309,16 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>0.74308</v>
       </c>
       <c r="L55">
-        <v>0.74035</v>
+        <v>0</v>
       </c>
       <c r="M55">
-        <v>0.00915</v>
+        <v>0.1913</v>
       </c>
       <c r="N55">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -15700,7 +15336,7 @@
         <v>0</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>0.00933</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -15757,9 +15393,6 @@
         <v>0</v>
       </c>
       <c r="AM55">
-        <v>0</v>
-      </c>
-      <c r="AN55">
         <v>0</v>
       </c>
     </row>
@@ -15793,7 +15426,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>0.94294</v>
+        <v>0.94291</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -15814,13 +15447,13 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>0.05546</v>
       </c>
       <c r="Q56">
-        <v>0.05543</v>
+        <v>0.00162</v>
       </c>
       <c r="R56">
-        <v>0.00162</v>
+        <v>0</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -15883,9 +15516,6 @@
         <v>0</v>
       </c>
       <c r="AM56">
-        <v>0</v>
-      </c>
-      <c r="AN56">
         <v>0</v>
       </c>
     </row>
@@ -15901,7 +15531,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>0.19942</v>
+        <v>0.20632</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -15919,7 +15549,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>0.77399</v>
+        <v>0.76625</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -15949,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>0.02743</v>
       </c>
       <c r="T57">
-        <v>0.02659</v>
+        <v>0</v>
       </c>
       <c r="U57">
         <v>0</v>
@@ -16009,9 +15639,6 @@
         <v>0</v>
       </c>
       <c r="AM57">
-        <v>0</v>
-      </c>
-      <c r="AN57">
         <v>0</v>
       </c>
     </row>
@@ -16045,7 +15672,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>0.02343</v>
+        <v>0.02377</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -16066,10 +15693,10 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>0.7706499999999999</v>
       </c>
       <c r="Q58">
-        <v>0.77394</v>
+        <v>0</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -16123,10 +15750,10 @@
         <v>0</v>
       </c>
       <c r="AI58">
-        <v>0</v>
+        <v>0.20559</v>
       </c>
       <c r="AJ58">
-        <v>0.20264</v>
+        <v>0</v>
       </c>
       <c r="AK58">
         <v>0</v>
@@ -16135,9 +15762,6 @@
         <v>0</v>
       </c>
       <c r="AM58">
-        <v>0</v>
-      </c>
-      <c r="AN58">
         <v>0</v>
       </c>
     </row>
@@ -16153,10 +15777,10 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.03581</v>
+        <v>0.03588</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>0.00631</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -16171,10 +15795,10 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>0.00265</v>
+        <v>0.0027</v>
       </c>
       <c r="J59">
-        <v>0.00608</v>
+        <v>0</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -16186,16 +15810,16 @@
         <v>0</v>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>0.00156</v>
       </c>
       <c r="O59">
-        <v>0.00156</v>
+        <v>0.32029</v>
       </c>
       <c r="P59">
-        <v>0.32069</v>
+        <v>0.00505</v>
       </c>
       <c r="Q59">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -16216,7 +15840,7 @@
         <v>0</v>
       </c>
       <c r="X59">
-        <v>0.5841499999999999</v>
+        <v>0.58835</v>
       </c>
       <c r="Y59">
         <v>0</v>
@@ -16231,10 +15855,10 @@
         <v>0</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>0.03973</v>
       </c>
       <c r="AD59">
-        <v>0.03979</v>
+        <v>0</v>
       </c>
       <c r="AE59">
         <v>0</v>
@@ -16255,15 +15879,12 @@
         <v>0</v>
       </c>
       <c r="AK59">
-        <v>0.00415</v>
+        <v>0</v>
       </c>
       <c r="AL59">
         <v>0</v>
       </c>
       <c r="AM59">
-        <v>0</v>
-      </c>
-      <c r="AN59">
         <v>0</v>
       </c>
     </row>
@@ -16279,7 +15900,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.16561</v>
+        <v>0.16426</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -16300,25 +15921,25 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>0.83247</v>
       </c>
       <c r="K60">
-        <v>0.82052</v>
+        <v>0</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>0.0009700000000000001</v>
       </c>
       <c r="M60">
-        <v>0.0009700000000000001</v>
+        <v>0</v>
       </c>
       <c r="N60">
         <v>0</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>0.0023</v>
       </c>
       <c r="P60">
-        <v>0.00231</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -16333,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="U60">
-        <v>0.01059</v>
+        <v>0</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -16387,9 +16008,6 @@
         <v>0</v>
       </c>
       <c r="AM60">
-        <v>0</v>
-      </c>
-      <c r="AN60">
         <v>0</v>
       </c>
     </row>
@@ -16405,40 +16023,40 @@
         </is>
       </c>
       <c r="C61">
-        <v>0.97346</v>
+        <v>0.97505</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>0.00031</v>
       </c>
       <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
         <v>0.00045</v>
       </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
       <c r="G61">
-        <v>0.00203</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>0.0021</v>
       </c>
       <c r="I61">
         <v>0.00051</v>
       </c>
       <c r="J61">
-        <v>0.0003</v>
+        <v>0.00123</v>
       </c>
       <c r="K61">
-        <v>0.00124</v>
+        <v>0.008410000000000001</v>
       </c>
       <c r="L61">
-        <v>0.008240000000000001</v>
+        <v>0.00565</v>
       </c>
       <c r="M61">
-        <v>0.00619</v>
+        <v>0.00249</v>
       </c>
       <c r="N61">
-        <v>0.00246</v>
+        <v>0</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -16453,13 +16071,13 @@
         <v>0</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>0.00197</v>
       </c>
       <c r="T61">
-        <v>0.00195</v>
+        <v>0.00121</v>
       </c>
       <c r="U61">
-        <v>0.00211</v>
+        <v>0.00023</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -16474,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>0.00099</v>
+        <v>0</v>
       </c>
       <c r="AA61">
         <v>0</v>
@@ -16492,7 +16110,7 @@
         <v>0</v>
       </c>
       <c r="AF61">
-        <v>8.000000000000001E-05</v>
+        <v>0</v>
       </c>
       <c r="AG61">
         <v>0</v>
@@ -16507,15 +16125,12 @@
         <v>0</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>0.00039</v>
       </c>
       <c r="AL61">
         <v>0</v>
       </c>
       <c r="AM61">
-        <v>0</v>
-      </c>
-      <c r="AN61">
         <v>0</v>
       </c>
     </row>
@@ -16531,7 +16146,7 @@
         </is>
       </c>
       <c r="C62">
-        <v>0.00625</v>
+        <v>0.00624</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -16558,10 +16173,10 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>0.99376</v>
       </c>
       <c r="M62">
-        <v>0.99375</v>
+        <v>0</v>
       </c>
       <c r="N62">
         <v>0</v>
@@ -16639,9 +16254,6 @@
         <v>0</v>
       </c>
       <c r="AM62">
-        <v>0</v>
-      </c>
-      <c r="AN62">
         <v>0</v>
       </c>
     </row>
@@ -16657,7 +16269,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>0.99229</v>
+        <v>0.9944</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -16681,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>0.0056</v>
       </c>
       <c r="L63">
-        <v>0.00559</v>
+        <v>0</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -16711,7 +16323,7 @@
         <v>0</v>
       </c>
       <c r="U63">
-        <v>0.00212</v>
+        <v>0</v>
       </c>
       <c r="V63">
         <v>0</v>
@@ -16765,9 +16377,6 @@
         <v>0</v>
       </c>
       <c r="AM63">
-        <v>0</v>
-      </c>
-      <c r="AN63">
         <v>0</v>
       </c>
     </row>
@@ -16783,10 +16392,10 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.21132</v>
+        <v>0.20825</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>0.51701</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -16795,25 +16404,25 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>0.02427</v>
+        <v>0</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>0.02393</v>
       </c>
       <c r="I64">
         <v>0</v>
       </c>
       <c r="J64">
-        <v>0.52445</v>
+        <v>0</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>0.00048</v>
       </c>
       <c r="L64">
-        <v>0.00049</v>
+        <v>0.19574</v>
       </c>
       <c r="M64">
-        <v>0.18412</v>
+        <v>0</v>
       </c>
       <c r="N64">
         <v>0</v>
@@ -16837,7 +16446,7 @@
         <v>0</v>
       </c>
       <c r="U64">
-        <v>0.00719</v>
+        <v>0.00709</v>
       </c>
       <c r="V64">
         <v>0</v>
@@ -16858,10 +16467,10 @@
         <v>0</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>0.04749</v>
       </c>
       <c r="AC64">
-        <v>0.04816</v>
+        <v>0</v>
       </c>
       <c r="AD64">
         <v>0</v>
@@ -16891,9 +16500,6 @@
         <v>0</v>
       </c>
       <c r="AM64">
-        <v>0</v>
-      </c>
-      <c r="AN64">
         <v>0</v>
       </c>
     </row>
@@ -16912,7 +16518,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>0.04008</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -16930,19 +16536,19 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>0.04008</v>
+        <v>0</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>0.88528</v>
       </c>
       <c r="L65">
-        <v>0.88515</v>
+        <v>0</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>0.03652</v>
       </c>
       <c r="N65">
-        <v>0.03666</v>
+        <v>0</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -16960,7 +16566,7 @@
         <v>0</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>0.03811</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -17014,12 +16620,9 @@
         <v>0</v>
       </c>
       <c r="AL65">
-        <v>0.03811</v>
+        <v>0</v>
       </c>
       <c r="AM65">
-        <v>0</v>
-      </c>
-      <c r="AN65">
         <v>0</v>
       </c>
     </row>
@@ -17053,7 +16656,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>0.29855</v>
+        <v>0.30172</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -17065,10 +16668,10 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>0.31034</v>
       </c>
       <c r="N66">
-        <v>0.31304</v>
+        <v>0</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -17140,12 +16743,9 @@
         <v>0</v>
       </c>
       <c r="AL66">
-        <v>0</v>
+        <v>0.38793</v>
       </c>
       <c r="AM66">
-        <v>0.38841</v>
-      </c>
-      <c r="AN66">
         <v>0</v>
       </c>
     </row>

--- a/Deliverables/12S/regions/arctic/ADFG_12s_arctic_speciesxsamples.xlsx
+++ b/Deliverables/12S/regions/arctic/ADFG_12s_arctic_speciesxsamples.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AN66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -378,24 +378,24 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Platichthys stellatus</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Pungitius pungitius</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Myoxocephalus spp.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Osmerus mordax</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Platichthys stellatus</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Pungitius pungitius</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Myoxocephalus spp.</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Liparis spp.</t>
@@ -403,59 +403,59 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Clupea pallasii.1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Boreogadus saida</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Pleuronectes quadrituberculatus</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ASV18</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ASV20</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Leptoclinus maculatus</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Ammodytes hexapterus</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Gadus chalcogrammus</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Lepidopsetta spp.</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Liparis tunicatus</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Gymnocanthus tricuspis</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>ASV34</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ASV35</t>
@@ -483,70 +483,75 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Hexagrammos spp.</t>
+          <t>ASV45</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>Hexagrammos lagocephalus</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>Hemilepidotus spp.</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>ASV52</t>
-        </is>
-      </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>ASV51</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>Stichaeus punctatus</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Oncorhynchus keta</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>ASV64</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>ASV70</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>ASV65</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Nautichthys pribilovius</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Pholis clemensi</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Podothecus accipenserinus</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Gadus spp.</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>ASV141</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>ASV124</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
           <t>Sebastolobus spp.</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Cottus aleuticus</t>
         </is>
@@ -564,32 +569,32 @@
         </is>
       </c>
       <c r="C2">
-        <v>16233</v>
+        <v>16232</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2750</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>2750</v>
-      </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>30</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
       <c r="L2">
         <v>0</v>
       </c>
@@ -672,6 +677,9 @@
         <v>0</v>
       </c>
       <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
         <v>0</v>
       </c>
     </row>
@@ -708,26 +716,26 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>1344</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1346</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
         <v>3</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
       <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>26</v>
       </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
       <c r="Q3">
         <v>0</v>
       </c>
@@ -786,15 +794,18 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
         <v>0</v>
       </c>
     </row>
@@ -810,7 +821,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>6397</v>
+        <v>6398</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -846,11 +857,11 @@
         <v>0</v>
       </c>
       <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>36</v>
       </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
       <c r="Q4">
         <v>0</v>
       </c>
@@ -918,6 +929,9 @@
         <v>0</v>
       </c>
       <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
         <v>0</v>
       </c>
     </row>
@@ -1043,6 +1057,9 @@
       <c r="AM5">
         <v>0</v>
       </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1068,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>4418</v>
       </c>
       <c r="H6">
-        <v>4419</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1104,10 +1121,10 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>3781</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3829</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -1164,6 +1181,9 @@
         <v>0</v>
       </c>
       <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
         <v>0</v>
       </c>
     </row>
@@ -1185,25 +1205,25 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>726</v>
       </c>
       <c r="H7">
-        <v>726</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>7</v>
       </c>
       <c r="J7">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1221,11 +1241,11 @@
         <v>0</v>
       </c>
       <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
         <v>27</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
       <c r="S7">
         <v>0</v>
       </c>
@@ -1287,6 +1307,9 @@
         <v>0</v>
       </c>
       <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
         <v>0</v>
       </c>
     </row>
@@ -1308,10 +1331,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="F8">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1326,23 +1349,23 @@
         <v>0</v>
       </c>
       <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>226</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
       <c r="M8">
-        <v>9364</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>623</v>
+        <v>9368</v>
       </c>
       <c r="O8">
+        <v>622</v>
+      </c>
+      <c r="P8">
         <v>318</v>
       </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
       <c r="Q8">
         <v>0</v>
       </c>
@@ -1350,10 +1373,10 @@
         <v>0</v>
       </c>
       <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
         <v>116</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -1410,6 +1433,9 @@
         <v>0</v>
       </c>
       <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
         <v>0</v>
       </c>
     </row>
@@ -1437,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>12174</v>
       </c>
       <c r="H9">
-        <v>12174</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1455,16 +1481,16 @@
         <v>0</v>
       </c>
       <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
         <v>762</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>1349</v>
       </c>
-      <c r="O9">
-        <v>5702</v>
-      </c>
       <c r="P9">
-        <v>0</v>
+        <v>5771</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1473,10 +1499,10 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="U9">
         <v>0</v>
@@ -1494,7 +1520,7 @@
         <v>405</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>0</v>
@@ -1503,11 +1529,11 @@
         <v>0</v>
       </c>
       <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
         <v>321</v>
       </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
       <c r="AE9">
         <v>0</v>
       </c>
@@ -1533,6 +1559,9 @@
         <v>0</v>
       </c>
       <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
         <v>0</v>
       </c>
     </row>
@@ -1548,23 +1577,23 @@
         </is>
       </c>
       <c r="C10">
-        <v>132972</v>
+        <v>133178</v>
       </c>
       <c r="D10">
-        <v>886269</v>
+        <v>884873</v>
       </c>
       <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>55</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
       <c r="I10">
         <v>0</v>
       </c>
@@ -1578,11 +1607,11 @@
         <v>0</v>
       </c>
       <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
         <v>57</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
       <c r="O10">
         <v>0</v>
       </c>
@@ -1656,6 +1685,9 @@
         <v>0</v>
       </c>
       <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
         <v>0</v>
       </c>
     </row>
@@ -1701,11 +1733,11 @@
         <v>0</v>
       </c>
       <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
         <v>195</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
       <c r="O11">
         <v>0</v>
       </c>
@@ -1779,6 +1811,9 @@
         <v>0</v>
       </c>
       <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
         <v>0</v>
       </c>
     </row>
@@ -1794,13 +1829,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>332771</v>
+        <v>334646</v>
       </c>
       <c r="D12">
-        <v>342865</v>
+        <v>342986</v>
       </c>
       <c r="E12">
-        <v>140324</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1809,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>140933</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1902,6 +1937,9 @@
         <v>0</v>
       </c>
       <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
         <v>0</v>
       </c>
     </row>
@@ -1923,17 +1961,17 @@
         <v>12851</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>3640</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
       <c r="I13">
         <v>0</v>
       </c>
@@ -2025,6 +2063,9 @@
         <v>0</v>
       </c>
       <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
         <v>0</v>
       </c>
     </row>
@@ -2061,11 +2102,11 @@
         <v>0</v>
       </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>35</v>
       </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
       <c r="L14">
         <v>0</v>
       </c>
@@ -2148,6 +2189,9 @@
         <v>0</v>
       </c>
       <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
         <v>0</v>
       </c>
     </row>
@@ -2166,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>8215</v>
+        <v>8218</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2271,6 +2315,9 @@
         <v>0</v>
       </c>
       <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
         <v>0</v>
       </c>
     </row>
@@ -2286,13 +2333,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>8623</v>
+        <v>8622</v>
       </c>
       <c r="D16">
         <v>5842</v>
       </c>
       <c r="E16">
-        <v>16149</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2301,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>16211</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2394,6 +2441,9 @@
         <v>0</v>
       </c>
       <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
         <v>0</v>
       </c>
     </row>
@@ -2481,11 +2531,11 @@
         <v>0</v>
       </c>
       <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
         <v>2483</v>
       </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
       <c r="AC17">
         <v>0</v>
       </c>
@@ -2517,6 +2567,9 @@
         <v>0</v>
       </c>
       <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
         <v>0</v>
       </c>
     </row>
@@ -2544,10 +2597,10 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="H18">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -2562,14 +2615,14 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="N18">
+        <v>567</v>
+      </c>
+      <c r="O18">
         <v>2042</v>
       </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
       <c r="P18">
         <v>0</v>
       </c>
@@ -2598,17 +2651,17 @@
         <v>0</v>
       </c>
       <c r="Y18">
-        <v>4230</v>
+        <v>4229</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
         <v>4</v>
       </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
       <c r="AC18">
         <v>0</v>
       </c>
@@ -2616,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="AE18">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -2640,6 +2693,9 @@
         <v>0</v>
       </c>
       <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
         <v>0</v>
       </c>
     </row>
@@ -2661,16 +2717,16 @@
         <v>170</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>4275</v>
       </c>
       <c r="F19">
-        <v>4218</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>5062</v>
       </c>
       <c r="H19">
-        <v>5063</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2685,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -2763,6 +2819,9 @@
         <v>0</v>
       </c>
       <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
         <v>0</v>
       </c>
     </row>
@@ -2808,17 +2867,17 @@
         <v>0</v>
       </c>
       <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
         <v>1674</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>53</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>10</v>
       </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
       <c r="Q20">
         <v>0</v>
       </c>
@@ -2886,6 +2945,9 @@
         <v>0</v>
       </c>
       <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
         <v>0</v>
       </c>
     </row>
@@ -2913,13 +2975,13 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>8646</v>
       </c>
       <c r="H21">
-        <v>8616</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>4133</v>
+        <v>4129</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2940,17 +3002,17 @@
         <v>0</v>
       </c>
       <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
         <v>328</v>
       </c>
-      <c r="Q21">
-        <v>1811</v>
-      </c>
       <c r="R21">
+        <v>1843</v>
+      </c>
+      <c r="S21">
         <v>626</v>
       </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
       <c r="T21">
         <v>0</v>
       </c>
@@ -2991,11 +3053,11 @@
         <v>0</v>
       </c>
       <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
         <v>339</v>
       </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
       <c r="AI21">
         <v>0</v>
       </c>
@@ -3009,6 +3071,9 @@
         <v>0</v>
       </c>
       <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
         <v>0</v>
       </c>
     </row>
@@ -3036,10 +3101,10 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>3163</v>
       </c>
       <c r="H22">
-        <v>3159</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -3054,17 +3119,17 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>664</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>1365</v>
+        <v>668</v>
       </c>
       <c r="O22">
+        <v>1358</v>
+      </c>
+      <c r="P22">
         <v>678</v>
       </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
       <c r="Q22">
         <v>0</v>
       </c>
@@ -3072,11 +3137,11 @@
         <v>0</v>
       </c>
       <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
         <v>1155</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
         <v>0</v>
       </c>
@@ -3093,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="AA22">
         <v>0</v>
@@ -3108,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -3126,12 +3191,15 @@
         <v>0</v>
       </c>
       <c r="AK22">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
         <v>0</v>
       </c>
     </row>
@@ -3147,7 +3215,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>4082</v>
+        <v>4087</v>
       </c>
       <c r="D23">
         <v>13232</v>
@@ -3255,6 +3323,9 @@
         <v>0</v>
       </c>
       <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
         <v>0</v>
       </c>
     </row>
@@ -3303,16 +3374,16 @@
         <v>0</v>
       </c>
       <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
         <v>7</v>
       </c>
-      <c r="O24">
-        <v>7820</v>
-      </c>
       <c r="P24">
-        <v>1007</v>
+        <v>7819</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>986</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -3378,6 +3449,9 @@
         <v>0</v>
       </c>
       <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
         <v>0</v>
       </c>
     </row>
@@ -3393,46 +3467,46 @@
         </is>
       </c>
       <c r="C25">
-        <v>7877</v>
+        <v>7876</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
+        <v>35</v>
+      </c>
+      <c r="F25">
+        <v>36</v>
+      </c>
+      <c r="G25">
+        <v>11</v>
+      </c>
+      <c r="H25">
         <v>1725</v>
       </c>
-      <c r="F25">
-        <v>35</v>
-      </c>
-      <c r="G25">
-        <v>36</v>
-      </c>
-      <c r="H25">
-        <v>11</v>
-      </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>396</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>321</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
       <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
         <v>511</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
       <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
         <v>33</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -3471,17 +3545,17 @@
         <v>0</v>
       </c>
       <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
         <v>127</v>
       </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
       <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
         <v>70</v>
       </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
       <c r="AG25">
         <v>0</v>
       </c>
@@ -3501,6 +3575,9 @@
         <v>0</v>
       </c>
       <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
         <v>0</v>
       </c>
     </row>
@@ -3519,19 +3596,19 @@
         <v>137</v>
       </c>
       <c r="D26">
-        <v>9214</v>
+        <v>9221</v>
       </c>
       <c r="E26">
-        <v>617</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="H26">
-        <v>267</v>
+        <v>618</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -3624,6 +3701,9 @@
         <v>0</v>
       </c>
       <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
         <v>0</v>
       </c>
     </row>
@@ -3639,7 +3719,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>8099</v>
+        <v>8160</v>
       </c>
       <c r="D27">
         <v>12824</v>
@@ -3651,10 +3731,10 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H27">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -3669,11 +3749,11 @@
         <v>0</v>
       </c>
       <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
         <v>114</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
       <c r="O27">
         <v>0</v>
       </c>
@@ -3747,6 +3827,9 @@
         <v>0</v>
       </c>
       <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
         <v>0</v>
       </c>
     </row>
@@ -3768,17 +3851,17 @@
         <v>143</v>
       </c>
       <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>50</v>
       </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
       <c r="I28">
         <v>0</v>
       </c>
@@ -3870,6 +3953,9 @@
         <v>0</v>
       </c>
       <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
         <v>0</v>
       </c>
     </row>
@@ -3912,11 +3998,11 @@
         <v>0</v>
       </c>
       <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
         <v>6</v>
       </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
       <c r="N29">
         <v>0</v>
       </c>
@@ -3924,11 +4010,11 @@
         <v>0</v>
       </c>
       <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
         <v>2669</v>
       </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
       <c r="R29">
         <v>0</v>
       </c>
@@ -3993,6 +4079,9 @@
         <v>0</v>
       </c>
       <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
         <v>0</v>
       </c>
     </row>
@@ -4020,35 +4109,35 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1839</v>
       </c>
       <c r="H30">
-        <v>1838</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>182</v>
       </c>
       <c r="J30">
-        <v>1973</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1974</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
         <v>690</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>1729</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>572</v>
       </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
       <c r="Q30">
         <v>0</v>
       </c>
@@ -4056,13 +4145,13 @@
         <v>0</v>
       </c>
       <c r="S30">
-        <v>1928</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>1932</v>
       </c>
       <c r="U30">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -4083,10 +4172,10 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -4116,6 +4205,9 @@
         <v>0</v>
       </c>
       <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
         <v>0</v>
       </c>
     </row>
@@ -4143,19 +4235,19 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>6249</v>
       </c>
       <c r="H31">
-        <v>6343</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>7</v>
       </c>
       <c r="J31">
-        <v>38316</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>38099</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4164,10 +4256,10 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1845</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -4179,13 +4271,13 @@
         <v>0</v>
       </c>
       <c r="S31">
-        <v>1385</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>906</v>
+        <v>1383</v>
       </c>
       <c r="U31">
-        <v>49</v>
+        <v>190</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -4200,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>908</v>
       </c>
       <c r="AA31">
         <v>0</v>
@@ -4209,19 +4301,19 @@
         <v>0</v>
       </c>
       <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
         <v>43</v>
       </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>2122</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2117</v>
       </c>
       <c r="AH31">
         <v>0</v>
@@ -4239,6 +4331,9 @@
         <v>0</v>
       </c>
       <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
         <v>0</v>
       </c>
     </row>
@@ -4266,19 +4361,19 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>31636</v>
       </c>
       <c r="H32">
-        <v>32055</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>155</v>
       </c>
       <c r="J32">
-        <v>5252</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>5250</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4287,14 +4382,14 @@
         <v>0</v>
       </c>
       <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
         <v>1150</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>77</v>
       </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
       <c r="Q32">
         <v>0</v>
       </c>
@@ -4302,13 +4397,13 @@
         <v>0</v>
       </c>
       <c r="S32">
-        <v>2238</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2237</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -4323,19 +4418,19 @@
         <v>0</v>
       </c>
       <c r="Z32">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>1235</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1187</v>
       </c>
       <c r="AE32">
         <v>0</v>
@@ -4359,9 +4454,12 @@
         <v>0</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
         <v>0</v>
       </c>
     </row>
@@ -4389,35 +4487,35 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H33">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
         <v>4</v>
       </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
         <v>646</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>1311</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>505</v>
       </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
       <c r="Q33">
         <v>0</v>
       </c>
@@ -4425,11 +4523,11 @@
         <v>0</v>
       </c>
       <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
         <v>1499</v>
       </c>
-      <c r="T33">
-        <v>856</v>
-      </c>
       <c r="U33">
         <v>0</v>
       </c>
@@ -4446,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2293</v>
       </c>
       <c r="AA33">
         <v>0</v>
@@ -4461,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="AE33">
-        <v>1464</v>
+        <v>0</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -4485,6 +4583,9 @@
         <v>0</v>
       </c>
       <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
         <v>0</v>
       </c>
     </row>
@@ -4506,32 +4607,32 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1895</v>
       </c>
       <c r="F34">
-        <v>1895</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>2212</v>
       </c>
       <c r="H34">
-        <v>2212</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
         <v>2</v>
       </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
       <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
         <v>14</v>
       </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
       <c r="N34">
         <v>0</v>
       </c>
@@ -4569,16 +4670,16 @@
         <v>0</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -4608,6 +4709,9 @@
         <v>0</v>
       </c>
       <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
         <v>0</v>
       </c>
     </row>
@@ -4626,37 +4730,37 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>7963</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="F35">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="H35">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>7910</v>
       </c>
       <c r="K35">
-        <v>6946</v>
+        <v>0</v>
       </c>
       <c r="L35">
-        <v>37889</v>
+        <v>6885</v>
       </c>
       <c r="M35">
-        <v>487</v>
+        <v>43731</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -4665,16 +4769,16 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
       <c r="T35">
-        <v>6808</v>
+        <v>0</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -4692,16 +4796,16 @@
         <v>0</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>1511</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="AD35">
         <v>0</v>
@@ -4722,15 +4826,18 @@
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
         <v>0</v>
       </c>
     </row>
@@ -4749,37 +4856,37 @@
         <v>21</v>
       </c>
       <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>363</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>135</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
         <v>123</v>
       </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>379</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>134</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
         <v>10</v>
       </c>
-      <c r="M36">
-        <v>2358</v>
-      </c>
       <c r="N36">
-        <v>0</v>
+        <v>2332</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -4788,10 +4895,10 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>3597</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>3506</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -4854,6 +4961,9 @@
         <v>0</v>
       </c>
       <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
         <v>0</v>
       </c>
     </row>
@@ -4920,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>1475</v>
+        <v>0</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -4938,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>1473</v>
       </c>
       <c r="AA37">
         <v>0</v>
@@ -4974,9 +5084,12 @@
         <v>0</v>
       </c>
       <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
         <v>109</v>
       </c>
-      <c r="AM37">
+      <c r="AN37">
         <v>0</v>
       </c>
     </row>
@@ -4995,37 +5108,37 @@
         <v>19</v>
       </c>
       <c r="D38">
-        <v>38560</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F38">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>2316</v>
       </c>
       <c r="H38">
-        <v>2356</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>3963</v>
+        <v>3861</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>37052</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>869</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>377</v>
+        <v>1287</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5034,17 +5147,17 @@
         <v>0</v>
       </c>
       <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
         <v>421</v>
       </c>
-      <c r="R38">
-        <v>2080</v>
-      </c>
       <c r="S38">
+        <v>2088</v>
+      </c>
+      <c r="T38">
         <v>288</v>
       </c>
-      <c r="T38">
-        <v>951</v>
-      </c>
       <c r="U38">
         <v>0</v>
       </c>
@@ -5061,16 +5174,16 @@
         <v>0</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>971</v>
       </c>
       <c r="AA38">
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>3018</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3445</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5082,11 +5195,11 @@
         <v>0</v>
       </c>
       <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
         <v>225</v>
       </c>
-      <c r="AH38">
-        <v>0</v>
-      </c>
       <c r="AI38">
         <v>0</v>
       </c>
@@ -5100,6 +5213,9 @@
         <v>0</v>
       </c>
       <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
         <v>0</v>
       </c>
     </row>
@@ -5118,56 +5234,56 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>2370</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F39">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H39">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I39">
         <v>28</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>2362</v>
       </c>
       <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
         <v>112</v>
       </c>
-      <c r="L39">
-        <v>727</v>
-      </c>
       <c r="M39">
-        <v>0</v>
+        <v>1108</v>
       </c>
       <c r="N39">
         <v>0</v>
       </c>
       <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
         <v>43</v>
       </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
       <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
         <v>98</v>
       </c>
-      <c r="R39">
+      <c r="S39">
         <v>20</v>
       </c>
-      <c r="S39">
+      <c r="T39">
         <v>19</v>
       </c>
-      <c r="T39">
-        <v>421</v>
-      </c>
       <c r="U39">
         <v>0</v>
       </c>
@@ -5190,10 +5306,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -5205,11 +5321,11 @@
         <v>0</v>
       </c>
       <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
         <v>182</v>
       </c>
-      <c r="AH39">
-        <v>0</v>
-      </c>
       <c r="AI39">
         <v>0</v>
       </c>
@@ -5223,6 +5339,9 @@
         <v>0</v>
       </c>
       <c r="AM39">
+        <v>0</v>
+      </c>
+      <c r="AN39">
         <v>0</v>
       </c>
     </row>
@@ -5241,26 +5360,26 @@
         <v>0</v>
       </c>
       <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>40032</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>41</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
         <v>64</v>
       </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>40581</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>41</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
       <c r="K40">
         <v>0</v>
       </c>
@@ -5268,10 +5387,10 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>701</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -5346,6 +5465,9 @@
         <v>0</v>
       </c>
       <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40">
         <v>0</v>
       </c>
     </row>
@@ -5364,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>3598</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5373,38 +5495,38 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>10642</v>
       </c>
       <c r="H41">
-        <v>10865</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>10476</v>
+        <v>10466</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>3541</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
         <v>26</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>15</v>
       </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
       <c r="R41">
         <v>0</v>
       </c>
@@ -5412,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -5430,19 +5552,19 @@
         <v>0</v>
       </c>
       <c r="Z41">
-        <v>5591</v>
+        <v>6573</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>5532</v>
       </c>
       <c r="AB41">
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>663</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -5451,13 +5573,13 @@
         <v>0</v>
       </c>
       <c r="AG41">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="AH41">
-        <v>960</v>
+        <v>359</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AJ41">
         <v>0</v>
@@ -5469,6 +5591,9 @@
         <v>0</v>
       </c>
       <c r="AM41">
+        <v>0</v>
+      </c>
+      <c r="AN41">
         <v>0</v>
       </c>
     </row>
@@ -5487,34 +5612,34 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>5989</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="F42">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>23214</v>
       </c>
       <c r="H42">
-        <v>23473</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>3215</v>
+        <v>3157</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>5981</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>4252</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -5523,19 +5648,19 @@
         <v>0</v>
       </c>
       <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
         <v>93</v>
       </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
       <c r="R42">
         <v>0</v>
       </c>
       <c r="S42">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>4424</v>
+        <v>142</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -5553,16 +5678,16 @@
         <v>0</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AA42">
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>2590</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2589</v>
       </c>
       <c r="AD42">
         <v>0</v>
@@ -5574,10 +5699,10 @@
         <v>0</v>
       </c>
       <c r="AG42">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AI42">
         <v>0</v>
@@ -5592,6 +5717,9 @@
         <v>0</v>
       </c>
       <c r="AM42">
+        <v>0</v>
+      </c>
+      <c r="AN42">
         <v>0</v>
       </c>
     </row>
@@ -5610,55 +5738,55 @@
         <v>0</v>
       </c>
       <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>562</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>135</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>2164</v>
+      </c>
+      <c r="J43">
         <v>244</v>
       </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>567</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>134</v>
-      </c>
-      <c r="I43">
-        <v>2168</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
       <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
         <v>653</v>
       </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
       <c r="M43">
-        <v>4704</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>8606</v>
+        <v>4744</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>8382</v>
       </c>
       <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
         <v>868</v>
       </c>
-      <c r="Q43">
-        <v>791</v>
-      </c>
       <c r="R43">
-        <v>0</v>
+        <v>753</v>
       </c>
       <c r="S43">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -5691,10 +5819,10 @@
         <v>0</v>
       </c>
       <c r="AE43">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1562</v>
       </c>
       <c r="AG43">
         <v>0</v>
@@ -5709,12 +5837,15 @@
         <v>0</v>
       </c>
       <c r="AK43">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL43">
+        <v>198</v>
+      </c>
+      <c r="AM43">
         <v>41</v>
       </c>
-      <c r="AM43">
+      <c r="AN43">
         <v>0</v>
       </c>
     </row>
@@ -5736,34 +5867,34 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>9792</v>
       </c>
       <c r="F44">
-        <v>9795</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1925</v>
       </c>
       <c r="H44">
-        <v>1926</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
         <v>83</v>
       </c>
-      <c r="K44">
-        <v>2505</v>
-      </c>
       <c r="L44">
-        <v>1491</v>
+        <v>2506</v>
       </c>
       <c r="M44">
-        <v>652</v>
+        <v>1532</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -5781,7 +5912,7 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="U44">
         <v>0</v>
@@ -5799,17 +5930,17 @@
         <v>0</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="AA44">
         <v>0</v>
       </c>
       <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
         <v>764</v>
       </c>
-      <c r="AC44">
-        <v>0</v>
-      </c>
       <c r="AD44">
         <v>0</v>
       </c>
@@ -5838,6 +5969,9 @@
         <v>0</v>
       </c>
       <c r="AM44">
+        <v>0</v>
+      </c>
+      <c r="AN44">
         <v>0</v>
       </c>
     </row>
@@ -5859,10 +5993,10 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1314</v>
       </c>
       <c r="F45">
-        <v>1415</v>
+        <v>0</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5871,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>15242</v>
+        <v>14860</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -5883,31 +6017,31 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>16012</v>
+        <v>0</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>16089</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>14393</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>13252</v>
+        <v>14190</v>
       </c>
       <c r="R45">
-        <v>13601</v>
+        <v>13109</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>13861</v>
       </c>
       <c r="T45">
         <v>0</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -5922,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="AA45">
         <v>0</v>
@@ -5937,10 +6071,10 @@
         <v>0</v>
       </c>
       <c r="AE45">
-        <v>1246</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>766</v>
       </c>
       <c r="AG45">
         <v>0</v>
@@ -5952,15 +6086,18 @@
         <v>0</v>
       </c>
       <c r="AJ45">
-        <v>557</v>
+        <v>0</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>742</v>
       </c>
       <c r="AL45">
         <v>0</v>
       </c>
       <c r="AM45">
+        <v>0</v>
+      </c>
+      <c r="AN45">
         <v>0</v>
       </c>
     </row>
@@ -5979,55 +6116,55 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>7323</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>11391</v>
       </c>
       <c r="F46">
-        <v>11604</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H46">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>2161</v>
+        <v>2136</v>
       </c>
       <c r="J46">
+        <v>7315</v>
+      </c>
+      <c r="K46">
         <v>72</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>135</v>
       </c>
-      <c r="L46">
-        <v>199</v>
-      </c>
       <c r="M46">
-        <v>20614</v>
+        <v>553</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>20456</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
         <v>61</v>
       </c>
-      <c r="R46">
-        <v>2015</v>
-      </c>
       <c r="S46">
-        <v>523</v>
+        <v>1998</v>
       </c>
       <c r="T46">
-        <v>566</v>
+        <v>513</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -6045,16 +6182,16 @@
         <v>0</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AA46">
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -6069,21 +6206,24 @@
         <v>0</v>
       </c>
       <c r="AH46">
+        <v>0</v>
+      </c>
+      <c r="AI46">
         <v>71</v>
       </c>
-      <c r="AI46">
-        <v>0</v>
-      </c>
       <c r="AJ46">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="AL46">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AM46">
+        <v>0</v>
+      </c>
+      <c r="AN46">
         <v>0</v>
       </c>
     </row>
@@ -6105,10 +6245,10 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -6129,28 +6269,28 @@
         <v>0</v>
       </c>
       <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
         <v>180</v>
       </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
         <v>78</v>
       </c>
-      <c r="Q47">
-        <v>348</v>
-      </c>
       <c r="R47">
+        <v>347</v>
+      </c>
+      <c r="S47">
         <v>38</v>
       </c>
-      <c r="S47">
-        <v>156</v>
-      </c>
       <c r="T47">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -6171,11 +6311,11 @@
         <v>0</v>
       </c>
       <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
         <v>1029</v>
       </c>
-      <c r="AB47">
-        <v>0</v>
-      </c>
       <c r="AC47">
         <v>0</v>
       </c>
@@ -6207,6 +6347,9 @@
         <v>0</v>
       </c>
       <c r="AM47">
+        <v>0</v>
+      </c>
+      <c r="AN47">
         <v>0</v>
       </c>
     </row>
@@ -6228,16 +6371,16 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="F48">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H48">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -6246,16 +6389,16 @@
         <v>0</v>
       </c>
       <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
         <v>578</v>
       </c>
-      <c r="L48">
+      <c r="M48">
         <v>465</v>
       </c>
-      <c r="M48">
-        <v>1355</v>
-      </c>
       <c r="N48">
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -6270,11 +6413,11 @@
         <v>0</v>
       </c>
       <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
         <v>331</v>
       </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
       <c r="U48">
         <v>0</v>
       </c>
@@ -6321,15 +6464,18 @@
         <v>0</v>
       </c>
       <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
         <v>100</v>
       </c>
-      <c r="AK48">
-        <v>0</v>
-      </c>
       <c r="AL48">
         <v>0</v>
       </c>
       <c r="AM48">
+        <v>0</v>
+      </c>
+      <c r="AN48">
         <v>54</v>
       </c>
     </row>
@@ -6348,55 +6494,55 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="F49">
-        <v>771</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>2797</v>
       </c>
       <c r="H49">
-        <v>2833</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>832</v>
+        <v>678</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="K49">
-        <v>9087</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>6386</v>
+        <v>9095</v>
       </c>
       <c r="M49">
-        <v>2251</v>
+        <v>7502</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2236</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="R49">
         <v>0</v>
       </c>
       <c r="S49">
-        <v>3105</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>1999</v>
+        <v>3065</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -6414,26 +6560,26 @@
         <v>0</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="AA49">
         <v>0</v>
       </c>
       <c r="AB49">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD49">
         <v>0</v>
       </c>
       <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
         <v>47</v>
       </c>
-      <c r="AF49">
-        <v>0</v>
-      </c>
       <c r="AG49">
         <v>0</v>
       </c>
@@ -6453,6 +6599,9 @@
         <v>0</v>
       </c>
       <c r="AM49">
+        <v>0</v>
+      </c>
+      <c r="AN49">
         <v>0</v>
       </c>
     </row>
@@ -6474,10 +6623,10 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>25665</v>
       </c>
       <c r="F50">
-        <v>25848</v>
+        <v>0</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -6492,16 +6641,16 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="M50">
-        <v>2587</v>
+        <v>0</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2849</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -6576,6 +6725,9 @@
         <v>0</v>
       </c>
       <c r="AM50">
+        <v>0</v>
+      </c>
+      <c r="AN50">
         <v>0</v>
       </c>
     </row>
@@ -6603,32 +6755,32 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H51">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>1676</v>
+        <v>0</v>
       </c>
       <c r="K51">
+        <v>1662</v>
+      </c>
+      <c r="L51">
         <v>81</v>
       </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
       <c r="M51">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
         <v>37</v>
       </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
       <c r="P51">
         <v>0</v>
       </c>
@@ -6642,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="T51">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>10371</v>
+        <v>10215</v>
       </c>
       <c r="V51">
         <v>0</v>
@@ -6699,6 +6851,9 @@
         <v>0</v>
       </c>
       <c r="AM51">
+        <v>0</v>
+      </c>
+      <c r="AN51">
         <v>0</v>
       </c>
     </row>
@@ -6720,10 +6875,10 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -6735,20 +6890,20 @@
         <v>0</v>
       </c>
       <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
         <v>4859</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <v>921</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>54</v>
       </c>
-      <c r="M52">
+      <c r="N52">
         <v>187</v>
       </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
       <c r="O52">
         <v>0</v>
       </c>
@@ -6768,7 +6923,7 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -6822,6 +6977,9 @@
         <v>0</v>
       </c>
       <c r="AM52">
+        <v>0</v>
+      </c>
+      <c r="AN52">
         <v>0</v>
       </c>
     </row>
@@ -6837,7 +6995,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -6846,37 +7004,37 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1139</v>
       </c>
       <c r="G53">
-        <v>1140</v>
+        <v>398</v>
       </c>
       <c r="H53">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="I53">
         <v>0</v>
       </c>
       <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
         <v>121</v>
       </c>
-      <c r="K53">
+      <c r="L53">
         <v>38</v>
       </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
       <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
         <v>52</v>
       </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
       <c r="O53">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -6897,7 +7055,7 @@
         <v>0</v>
       </c>
       <c r="W53">
-        <v>6672</v>
+        <v>6615</v>
       </c>
       <c r="X53">
         <v>0</v>
@@ -6918,10 +7076,10 @@
         <v>0</v>
       </c>
       <c r="AD53">
-        <v>1378</v>
+        <v>0</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1368</v>
       </c>
       <c r="AF53">
         <v>0</v>
@@ -6945,6 +7103,9 @@
         <v>0</v>
       </c>
       <c r="AM53">
+        <v>0</v>
+      </c>
+      <c r="AN53">
         <v>0</v>
       </c>
     </row>
@@ -6966,19 +7127,19 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>2321</v>
       </c>
       <c r="F54">
-        <v>2343</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1851</v>
       </c>
       <c r="H54">
-        <v>1861</v>
+        <v>0</v>
       </c>
       <c r="I54">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -6987,16 +7148,16 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="N54">
-        <v>1335</v>
+        <v>74</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>1310</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -7008,16 +7169,16 @@
         <v>0</v>
       </c>
       <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
         <v>95</v>
       </c>
-      <c r="T54">
-        <v>76</v>
-      </c>
       <c r="U54">
         <v>0</v>
       </c>
       <c r="V54">
-        <v>10026</v>
+        <v>9891</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -7029,7 +7190,7 @@
         <v>0</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA54">
         <v>0</v>
@@ -7062,12 +7223,15 @@
         <v>0</v>
       </c>
       <c r="AK54">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="AL54">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="AM54">
+        <v>0</v>
+      </c>
+      <c r="AN54">
         <v>0</v>
       </c>
     </row>
@@ -7089,16 +7253,16 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>618</v>
       </c>
       <c r="H55">
-        <v>618</v>
+        <v>532</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -7107,16 +7271,16 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>24044</v>
+        <v>0</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>23874</v>
       </c>
       <c r="M55">
-        <v>6190</v>
+        <v>295</v>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>6256</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -7134,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="T55">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -7191,6 +7355,9 @@
         <v>0</v>
       </c>
       <c r="AM55">
+        <v>0</v>
+      </c>
+      <c r="AN55">
         <v>0</v>
       </c>
     </row>
@@ -7224,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>35992</v>
+        <v>36012</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -7245,14 +7412,14 @@
         <v>0</v>
       </c>
       <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
         <v>2117</v>
       </c>
-      <c r="Q56">
+      <c r="R56">
         <v>62</v>
       </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
       <c r="S56">
         <v>0</v>
       </c>
@@ -7314,6 +7481,9 @@
         <v>0</v>
       </c>
       <c r="AM56">
+        <v>0</v>
+      </c>
+      <c r="AN56">
         <v>0</v>
       </c>
     </row>
@@ -7329,7 +7499,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -7347,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>1285</v>
+        <v>1339</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -7377,11 +7547,11 @@
         <v>0</v>
       </c>
       <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
         <v>46</v>
       </c>
-      <c r="T57">
-        <v>0</v>
-      </c>
       <c r="U57">
         <v>0</v>
       </c>
@@ -7437,6 +7607,9 @@
         <v>0</v>
       </c>
       <c r="AM57">
+        <v>0</v>
+      </c>
+      <c r="AN57">
         <v>0</v>
       </c>
     </row>
@@ -7491,10 +7664,10 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>2594</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2643</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -7548,11 +7721,11 @@
         <v>0</v>
       </c>
       <c r="AI58">
+        <v>0</v>
+      </c>
+      <c r="AJ58">
         <v>692</v>
       </c>
-      <c r="AJ58">
-        <v>0</v>
-      </c>
       <c r="AK58">
         <v>0</v>
       </c>
@@ -7560,6 +7733,9 @@
         <v>0</v>
       </c>
       <c r="AM58">
+        <v>0</v>
+      </c>
+      <c r="AN58">
         <v>0</v>
       </c>
     </row>
@@ -7575,10 +7751,10 @@
         </is>
       </c>
       <c r="C59">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D59">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -7593,10 +7769,10 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -7608,16 +7784,16 @@
         <v>0</v>
       </c>
       <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
         <v>26</v>
       </c>
-      <c r="O59">
-        <v>5329</v>
-      </c>
       <c r="P59">
-        <v>84</v>
+        <v>5328</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -7638,7 +7814,7 @@
         <v>0</v>
       </c>
       <c r="X59">
-        <v>9789</v>
+        <v>9705</v>
       </c>
       <c r="Y59">
         <v>0</v>
@@ -7653,11 +7829,11 @@
         <v>0</v>
       </c>
       <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
         <v>661</v>
       </c>
-      <c r="AD59">
-        <v>0</v>
-      </c>
       <c r="AE59">
         <v>0</v>
       </c>
@@ -7677,12 +7853,15 @@
         <v>0</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AL59">
         <v>0</v>
       </c>
       <c r="AM59">
+        <v>0</v>
+      </c>
+      <c r="AN59">
         <v>0</v>
       </c>
     </row>
@@ -7698,7 +7877,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -7719,26 +7898,26 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>6872</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>6743</v>
       </c>
       <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
         <v>8</v>
       </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
       <c r="N60">
         <v>0</v>
       </c>
       <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
         <v>19</v>
       </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
       <c r="Q60">
         <v>0</v>
       </c>
@@ -7752,7 +7931,7 @@
         <v>0</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -7806,6 +7985,9 @@
         <v>0</v>
       </c>
       <c r="AM60">
+        <v>0</v>
+      </c>
+      <c r="AN60">
         <v>0</v>
       </c>
     </row>
@@ -7821,41 +8003,41 @@
         </is>
       </c>
       <c r="C61">
-        <v>47438</v>
+        <v>47972</v>
       </c>
       <c r="D61">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F61">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <v>25</v>
       </c>
       <c r="J61">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K61">
-        <v>409</v>
+        <v>61</v>
       </c>
       <c r="L61">
-        <v>275</v>
+        <v>406</v>
       </c>
       <c r="M61">
+        <v>305</v>
+      </c>
+      <c r="N61">
         <v>121</v>
       </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
       <c r="O61">
         <v>0</v>
       </c>
@@ -7869,13 +8051,13 @@
         <v>0</v>
       </c>
       <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
         <v>96</v>
       </c>
-      <c r="T61">
-        <v>59</v>
-      </c>
       <c r="U61">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -7890,7 +8072,7 @@
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AA61">
         <v>0</v>
@@ -7908,7 +8090,7 @@
         <v>0</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG61">
         <v>0</v>
@@ -7923,12 +8105,15 @@
         <v>0</v>
       </c>
       <c r="AK61">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AL61">
         <v>0</v>
       </c>
       <c r="AM61">
+        <v>0</v>
+      </c>
+      <c r="AN61">
         <v>0</v>
       </c>
     </row>
@@ -7971,10 +8156,10 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>2548</v>
+        <v>0</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>2545</v>
       </c>
       <c r="N62">
         <v>0</v>
@@ -8052,6 +8237,9 @@
         <v>0</v>
       </c>
       <c r="AM62">
+        <v>0</v>
+      </c>
+      <c r="AN62">
         <v>0</v>
       </c>
     </row>
@@ -8067,7 +8255,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>19343</v>
+        <v>19176</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -8091,10 +8279,10 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -8121,7 +8309,7 @@
         <v>0</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="V63">
         <v>0</v>
@@ -8175,6 +8363,9 @@
         <v>0</v>
       </c>
       <c r="AM63">
+        <v>0</v>
+      </c>
+      <c r="AN63">
         <v>0</v>
       </c>
     </row>
@@ -8190,10 +8381,10 @@
         </is>
       </c>
       <c r="C64">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="D64">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -8202,25 +8393,25 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="H64">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="I64">
         <v>0</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>4301</v>
       </c>
       <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
         <v>4</v>
       </c>
-      <c r="L64">
-        <v>1628</v>
-      </c>
       <c r="M64">
-        <v>0</v>
+        <v>1510</v>
       </c>
       <c r="N64">
         <v>0</v>
@@ -8265,11 +8456,11 @@
         <v>0</v>
       </c>
       <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
         <v>395</v>
       </c>
-      <c r="AC64">
-        <v>0</v>
-      </c>
       <c r="AD64">
         <v>0</v>
       </c>
@@ -8298,6 +8489,9 @@
         <v>0</v>
       </c>
       <c r="AM64">
+        <v>0</v>
+      </c>
+      <c r="AN64">
         <v>0</v>
       </c>
     </row>
@@ -8316,37 +8510,37 @@
         <v>0</v>
       </c>
       <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
         <v>304</v>
       </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
       <c r="K65">
-        <v>6714</v>
+        <v>0</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>6713</v>
       </c>
       <c r="M65">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -8364,63 +8558,66 @@
         <v>0</v>
       </c>
       <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65">
+        <v>0</v>
+      </c>
+      <c r="AI65">
+        <v>0</v>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
         <v>289</v>
       </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>0</v>
-      </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
-      </c>
-      <c r="AB65">
-        <v>0</v>
-      </c>
-      <c r="AC65">
-        <v>0</v>
-      </c>
-      <c r="AD65">
-        <v>0</v>
-      </c>
-      <c r="AE65">
-        <v>0</v>
-      </c>
-      <c r="AF65">
-        <v>0</v>
-      </c>
-      <c r="AG65">
-        <v>0</v>
-      </c>
-      <c r="AH65">
-        <v>0</v>
-      </c>
-      <c r="AI65">
-        <v>0</v>
-      </c>
-      <c r="AJ65">
-        <v>0</v>
-      </c>
-      <c r="AK65">
-        <v>0</v>
-      </c>
-      <c r="AL65">
-        <v>0</v>
-      </c>
       <c r="AM65">
+        <v>0</v>
+      </c>
+      <c r="AN65">
         <v>0</v>
       </c>
     </row>
@@ -8454,7 +8651,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -8466,11 +8663,11 @@
         <v>0</v>
       </c>
       <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
         <v>108</v>
       </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
       <c r="O66">
         <v>0</v>
       </c>
@@ -8541,9 +8738,12 @@
         <v>0</v>
       </c>
       <c r="AL66">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="AM66">
+        <v>134</v>
+      </c>
+      <c r="AN66">
         <v>0</v>
       </c>
     </row>
@@ -8554,7 +8754,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AN66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8580,24 +8780,24 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Platichthys stellatus</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Pungitius pungitius</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Myoxocephalus spp.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Osmerus mordax</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Platichthys stellatus</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Pungitius pungitius</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Myoxocephalus spp.</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Liparis spp.</t>
@@ -8605,59 +8805,59 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Clupea pallasii.1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Boreogadus saida</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Pleuronectes quadrituberculatus</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ASV18</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ASV20</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Leptoclinus maculatus</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Ammodytes hexapterus</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Gadus chalcogrammus</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Lepidopsetta spp.</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Liparis tunicatus</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Gymnocanthus tricuspis</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>ASV34</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ASV35</t>
@@ -8685,70 +8885,75 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Hexagrammos spp.</t>
+          <t>ASV45</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>Hexagrammos lagocephalus</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>Hemilepidotus spp.</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>ASV52</t>
-        </is>
-      </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>ASV51</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>Stichaeus punctatus</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Oncorhynchus keta</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>ASV64</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>ASV70</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>ASV65</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Nautichthys pribilovius</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Pholis clemensi</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Podothecus accipenserinus</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Gadus spp.</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>ASV141</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>ASV124</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
           <t>Sebastolobus spp.</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Cottus aleuticus</t>
         </is>
@@ -8766,32 +8971,32 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.85356</v>
+        <v>0.85355</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.14461</v>
+      </c>
+      <c r="H2">
         <v>0.00026</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0.1446</v>
-      </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>0.00158</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
       <c r="L2">
         <v>0</v>
       </c>
@@ -8874,6 +9079,9 @@
         <v>0</v>
       </c>
       <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
         <v>0</v>
       </c>
     </row>
@@ -8910,25 +9118,25 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0.95795</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.94655</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0.00214</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>0.00211</v>
       </c>
       <c r="O3">
-        <v>0.01853</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>0.01828</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -8988,15 +9196,18 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.02138</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>0.03305</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
         <v>0</v>
       </c>
     </row>
@@ -9048,11 +9259,11 @@
         <v>0</v>
       </c>
       <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>0.0056</v>
       </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
       <c r="Q4">
         <v>0</v>
       </c>
@@ -9120,6 +9331,9 @@
         <v>0</v>
       </c>
       <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
         <v>0</v>
       </c>
     </row>
@@ -9245,6 +9459,9 @@
       <c r="AM5">
         <v>0</v>
       </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9258,7 +9475,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.52523</v>
+        <v>0.5238</v>
       </c>
       <c r="D6">
         <v>0.00144</v>
@@ -9270,10 +9487,10 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.25433</v>
       </c>
       <c r="H6">
-        <v>0.25508</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -9306,10 +9523,10 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0.21825</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.22042</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -9366,6 +9583,9 @@
         <v>0</v>
       </c>
       <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
         <v>0</v>
       </c>
     </row>
@@ -9387,25 +9607,25 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>0.03129</v>
       </c>
       <c r="F7">
-        <v>0.03136</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.87365</v>
       </c>
       <c r="H7">
-        <v>0.87575</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.00844</v>
+        <v>0.00842</v>
       </c>
       <c r="J7">
-        <v>0.05187</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.05415</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -9423,10 +9643,10 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.03257</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.03249</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -9489,6 +9709,9 @@
         <v>0</v>
       </c>
       <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
         <v>0</v>
       </c>
     </row>
@@ -9510,10 +9733,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>0.02947</v>
       </c>
       <c r="F8">
-        <v>0.02957</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -9528,22 +9751,22 @@
         <v>0</v>
       </c>
       <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>0.02019</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
       <c r="M8">
-        <v>0.83652</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>0.05565</v>
+        <v>0.83673</v>
       </c>
       <c r="O8">
-        <v>0.02841</v>
+        <v>0.05556</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>0.0284</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -9552,10 +9775,10 @@
         <v>0</v>
       </c>
       <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
         <v>0.01036</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -9612,6 +9835,9 @@
         <v>0</v>
       </c>
       <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
         <v>0</v>
       </c>
     </row>
@@ -9639,10 +9865,10 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.5759</v>
       </c>
       <c r="H9">
-        <v>0.57787</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -9657,16 +9883,16 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0.03617</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>0.06403</v>
+        <v>0.03605</v>
       </c>
       <c r="O9">
-        <v>0.27066</v>
+        <v>0.06382</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -9675,29 +9901,29 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>0.01647</v>
+        <v>0</v>
       </c>
       <c r="T9">
+        <v>0.01656</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0.01916</v>
+      </c>
+      <c r="Z9">
         <v>0.00033</v>
       </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0.01922</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
       <c r="AA9">
         <v>0</v>
       </c>
@@ -9705,10 +9931,10 @@
         <v>0</v>
       </c>
       <c r="AC9">
-        <v>0.01524</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>0.01519</v>
       </c>
       <c r="AE9">
         <v>0</v>
@@ -9735,6 +9961,9 @@
         <v>0</v>
       </c>
       <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
         <v>0</v>
       </c>
     </row>
@@ -9750,23 +9979,23 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.13045</v>
+        <v>0.1308</v>
       </c>
       <c r="D10">
-        <v>0.86944</v>
+        <v>0.86909</v>
       </c>
       <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>5E-05</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
       <c r="I10">
         <v>0</v>
       </c>
@@ -9780,11 +10009,11 @@
         <v>0</v>
       </c>
       <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
         <v>6E-05</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
       <c r="O10">
         <v>0</v>
       </c>
@@ -9858,6 +10087,9 @@
         <v>0</v>
       </c>
       <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
         <v>0</v>
       </c>
     </row>
@@ -9903,11 +10135,11 @@
         <v>0</v>
       </c>
       <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
         <v>0.38614</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
       <c r="O11">
         <v>0</v>
       </c>
@@ -9981,6 +10213,9 @@
         <v>0</v>
       </c>
       <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
         <v>0</v>
       </c>
     </row>
@@ -9996,13 +10231,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.40783</v>
+        <v>0.40882</v>
       </c>
       <c r="D12">
-        <v>0.4202</v>
+        <v>0.41901</v>
       </c>
       <c r="E12">
-        <v>0.17197</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -10011,7 +10246,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>0.17217</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -10104,6 +10339,9 @@
         <v>0</v>
       </c>
       <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
         <v>0</v>
       </c>
     </row>
@@ -10125,17 +10363,17 @@
         <v>0.25862</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>0.07325</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
       <c r="I13">
         <v>0</v>
       </c>
@@ -10227,6 +10465,9 @@
         <v>0</v>
       </c>
       <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
         <v>0</v>
       </c>
     </row>
@@ -10263,11 +10504,11 @@
         <v>0</v>
       </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>0.00372</v>
       </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
       <c r="L14">
         <v>0</v>
       </c>
@@ -10350,6 +10591,9 @@
         <v>0</v>
       </c>
       <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
         <v>0</v>
       </c>
     </row>
@@ -10475,6 +10719,9 @@
       <c r="AM15">
         <v>0</v>
       </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10488,13 +10735,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.28167</v>
+        <v>0.28108</v>
       </c>
       <c r="D16">
-        <v>0.19083</v>
+        <v>0.19045</v>
       </c>
       <c r="E16">
-        <v>0.5275</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -10503,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>0.5284799999999999</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -10596,6 +10843,9 @@
         <v>0</v>
       </c>
       <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
         <v>0</v>
       </c>
     </row>
@@ -10683,11 +10933,11 @@
         <v>0</v>
       </c>
       <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
         <v>0.59559</v>
       </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
       <c r="AC17">
         <v>0</v>
       </c>
@@ -10719,6 +10969,9 @@
         <v>0</v>
       </c>
       <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
         <v>0</v>
       </c>
     </row>
@@ -10734,7 +10987,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.17945</v>
+        <v>0.17917</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -10746,10 +10999,10 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.04054</v>
       </c>
       <c r="H18">
-        <v>0.04072</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0.00079</v>
@@ -10764,13 +11017,13 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0.06215</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>0.23032</v>
+        <v>0.06385</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>0.22995</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -10800,17 +11053,17 @@
         <v>0</v>
       </c>
       <c r="Y18">
-        <v>0.4771</v>
+        <v>0.47624</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>0.009010000000000001</v>
       </c>
       <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
         <v>0.00045</v>
       </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
       <c r="AC18">
         <v>0</v>
       </c>
@@ -10818,7 +11071,7 @@
         <v>0</v>
       </c>
       <c r="AE18">
-        <v>0.00902</v>
+        <v>0</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -10842,6 +11095,9 @@
         <v>0</v>
       </c>
       <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
         <v>0</v>
       </c>
     </row>
@@ -10857,22 +11113,22 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.05526</v>
+        <v>0.0551</v>
       </c>
       <c r="D19">
-        <v>0.01693</v>
+        <v>0.01688</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>0.4244</v>
       </c>
       <c r="F19">
-        <v>0.41995</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>0.50253</v>
       </c>
       <c r="H19">
-        <v>0.50408</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -10887,7 +11143,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0.00269</v>
+        <v>0</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -10914,7 +11170,7 @@
         <v>0</v>
       </c>
       <c r="V19">
-        <v>0.0011</v>
+        <v>0.00109</v>
       </c>
       <c r="W19">
         <v>0</v>
@@ -10965,6 +11221,9 @@
         <v>0</v>
       </c>
       <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
         <v>0</v>
       </c>
     </row>
@@ -11010,17 +11269,17 @@
         <v>0</v>
       </c>
       <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
         <v>0.96373</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.03051</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.00576</v>
       </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
       <c r="Q20">
         <v>0</v>
       </c>
@@ -11088,6 +11347,9 @@
         <v>0</v>
       </c>
       <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
         <v>0</v>
       </c>
     </row>
@@ -11115,13 +11377,13 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>0.5434</v>
       </c>
       <c r="H21">
-        <v>0.54349</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>0.26071</v>
+        <v>0.25951</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -11142,16 +11404,16 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>0.02069</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>0.11424</v>
+        <v>0.02061</v>
       </c>
       <c r="R21">
-        <v>0.03949</v>
+        <v>0.11583</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>0.03934</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -11193,10 +11455,10 @@
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>0.02138</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>0.02131</v>
       </c>
       <c r="AI21">
         <v>0</v>
@@ -11211,6 +11473,9 @@
         <v>0</v>
       </c>
       <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
         <v>0</v>
       </c>
     </row>
@@ -11226,7 +11491,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.03035</v>
+        <v>0.03032</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -11238,10 +11503,10 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>0.40808</v>
       </c>
       <c r="H22">
-        <v>0.40798</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -11256,16 +11521,16 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0.08575000000000001</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>0.17629</v>
+        <v>0.08618000000000001</v>
       </c>
       <c r="O22">
-        <v>0.08756</v>
+        <v>0.1752</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>0.08747000000000001</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -11274,10 +11539,10 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>0.14917</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>0.14901</v>
       </c>
       <c r="U22">
         <v>0</v>
@@ -11295,7 +11560,7 @@
         <v>0</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>0.01561</v>
       </c>
       <c r="AA22">
         <v>0</v>
@@ -11310,7 +11575,7 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>0.01563</v>
+        <v>0</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -11328,12 +11593,15 @@
         <v>0</v>
       </c>
       <c r="AK22">
-        <v>0.04727</v>
+        <v>0</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>0.04812</v>
       </c>
       <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
         <v>0</v>
       </c>
     </row>
@@ -11349,10 +11617,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.23576</v>
+        <v>0.23598</v>
       </c>
       <c r="D23">
-        <v>0.76424</v>
+        <v>0.76402</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -11457,6 +11725,9 @@
         <v>0</v>
       </c>
       <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
         <v>0</v>
       </c>
     </row>
@@ -11472,7 +11743,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.01296</v>
+        <v>0.01299</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -11505,16 +11776,16 @@
         <v>0</v>
       </c>
       <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
         <v>0.00078</v>
       </c>
-      <c r="O24">
-        <v>0.87374</v>
-      </c>
       <c r="P24">
-        <v>0.11251</v>
+        <v>0.87578</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>0.11044</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -11580,6 +11851,9 @@
         <v>0</v>
       </c>
       <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
         <v>0</v>
       </c>
     </row>
@@ -11595,46 +11869,46 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.66115</v>
+        <v>0.66113</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0.14479</v>
+        <v>0.00294</v>
       </c>
       <c r="F25">
-        <v>0.00294</v>
+        <v>0.00302</v>
       </c>
       <c r="G25">
-        <v>0.00302</v>
+        <v>0.00092</v>
       </c>
       <c r="H25">
-        <v>0.00092</v>
+        <v>0.1448</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>0.03324</v>
       </c>
-      <c r="K25">
-        <v>0.02694</v>
-      </c>
       <c r="L25">
-        <v>0</v>
+        <v>0.02695</v>
       </c>
       <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
         <v>0.04289</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
       <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
         <v>0.00277</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -11673,17 +11947,17 @@
         <v>0</v>
       </c>
       <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
         <v>0.01066</v>
       </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
       <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
         <v>0.00588</v>
       </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
       <c r="AG25">
         <v>0</v>
       </c>
@@ -11703,6 +11977,9 @@
         <v>0</v>
       </c>
       <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
         <v>0</v>
       </c>
     </row>
@@ -11718,22 +11995,22 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.01339</v>
+        <v>0.01337</v>
       </c>
       <c r="D26">
-        <v>0.90024</v>
+        <v>0.90022</v>
       </c>
       <c r="E26">
-        <v>0.06028</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>0.02607</v>
       </c>
       <c r="H26">
-        <v>0.02609</v>
+        <v>0.06033</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -11826,6 +12103,9 @@
         <v>0</v>
       </c>
       <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
         <v>0</v>
       </c>
     </row>
@@ -11841,10 +12121,10 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.37518</v>
+        <v>0.37694</v>
       </c>
       <c r="D27">
-        <v>0.59406</v>
+        <v>0.59239</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -11853,10 +12133,10 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>0.02541</v>
       </c>
       <c r="H27">
-        <v>0.02548</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -11871,10 +12151,10 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0.00528</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>0.00527</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -11949,6 +12229,9 @@
         <v>0</v>
       </c>
       <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
         <v>0</v>
       </c>
     </row>
@@ -11970,17 +12253,17 @@
         <v>0.4511</v>
       </c>
       <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>0.15773</v>
       </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
       <c r="I28">
         <v>0</v>
       </c>
@@ -12072,6 +12355,9 @@
         <v>0</v>
       </c>
       <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
         <v>0</v>
       </c>
     </row>
@@ -12114,11 +12400,11 @@
         <v>0</v>
       </c>
       <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
         <v>0.00224</v>
       </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
       <c r="N29">
         <v>0</v>
       </c>
@@ -12126,11 +12412,11 @@
         <v>0</v>
       </c>
       <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
         <v>0.99776</v>
       </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
       <c r="R29">
         <v>0</v>
       </c>
@@ -12195,6 +12481,9 @@
         <v>0</v>
       </c>
       <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
         <v>0</v>
       </c>
     </row>
@@ -12222,34 +12511,34 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>0.1924</v>
       </c>
       <c r="H30">
-        <v>0.19242</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>0.01905</v>
+        <v>0.01904</v>
       </c>
       <c r="J30">
-        <v>0.20655</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>0.20653</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0.07224</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>0.18101</v>
+        <v>0.07219</v>
       </c>
       <c r="O30">
-        <v>0.05988</v>
+        <v>0.1809</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>0.05985</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -12258,13 +12547,13 @@
         <v>0</v>
       </c>
       <c r="S30">
-        <v>0.20184</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>0.20213</v>
       </c>
       <c r="U30">
-        <v>0.03706</v>
+        <v>0.03683</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -12285,10 +12574,10 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.02994</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>0.03013</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -12318,6 +12607,9 @@
         <v>0</v>
       </c>
       <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
         <v>0</v>
       </c>
     </row>
@@ -12345,19 +12637,19 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>0.12291</v>
       </c>
       <c r="H31">
-        <v>0.12429</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0.00014</v>
       </c>
       <c r="J31">
-        <v>0.75081</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>0.74938</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -12366,10 +12658,10 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>0.03649</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>0.03629</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -12381,13 +12673,13 @@
         <v>0</v>
       </c>
       <c r="S31">
-        <v>0.02714</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>0.01775</v>
+        <v>0.0272</v>
       </c>
       <c r="U31">
-        <v>0.00096</v>
+        <v>0.00374</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -12402,7 +12694,7 @@
         <v>0</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>0.01786</v>
       </c>
       <c r="AA31">
         <v>0</v>
@@ -12411,19 +12703,19 @@
         <v>0</v>
       </c>
       <c r="AC31">
-        <v>0.00084</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>0.00085</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>0.04158</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>0.04164</v>
       </c>
       <c r="AH31">
         <v>0</v>
@@ -12441,6 +12733,9 @@
         <v>0</v>
       </c>
       <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
         <v>0</v>
       </c>
     </row>
@@ -12468,19 +12763,19 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>0.7567700000000001</v>
       </c>
       <c r="H32">
-        <v>0.75637</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>0.00366</v>
+        <v>0.00371</v>
       </c>
       <c r="J32">
-        <v>0.12393</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>0.12559</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -12489,13 +12784,13 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>0.02714</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>0.00182</v>
+        <v>0.02751</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>0.00184</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -12504,13 +12799,13 @@
         <v>0</v>
       </c>
       <c r="S32">
-        <v>0.05281</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>0.05351</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>0.00167</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -12525,19 +12820,19 @@
         <v>0</v>
       </c>
       <c r="Z32">
-        <v>0.00399</v>
+        <v>0</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.00116</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>0.02914</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>0.02839</v>
       </c>
       <c r="AE32">
         <v>0</v>
@@ -12561,9 +12856,12 @@
         <v>0</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
         <v>0</v>
       </c>
     </row>
@@ -12591,34 +12889,34 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>0.00334</v>
       </c>
       <c r="H33">
-        <v>0.00333</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0.00063</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>0.0006400000000000001</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0.10244</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>0.2079</v>
+        <v>0.10288</v>
       </c>
       <c r="O33">
-        <v>0.08008</v>
+        <v>0.20879</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>0.08043</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -12627,10 +12925,10 @@
         <v>0</v>
       </c>
       <c r="S33">
-        <v>0.23771</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>0.13574</v>
+        <v>0.23873</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -12648,7 +12946,7 @@
         <v>0</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>0.36519</v>
       </c>
       <c r="AA33">
         <v>0</v>
@@ -12663,7 +12961,7 @@
         <v>0</v>
       </c>
       <c r="AE33">
-        <v>0.23216</v>
+        <v>0</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -12687,6 +12985,9 @@
         <v>0</v>
       </c>
       <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
         <v>0</v>
       </c>
     </row>
@@ -12708,32 +13009,32 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>0.43147</v>
       </c>
       <c r="F34">
-        <v>0.43147</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>0.50364</v>
       </c>
       <c r="H34">
-        <v>0.50364</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
         <v>0.00046</v>
       </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
       <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
         <v>0.00319</v>
       </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
       <c r="N34">
         <v>0</v>
       </c>
@@ -12771,16 +13072,16 @@
         <v>0</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>0.04463</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.06125</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>0.01662</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -12810,6 +13111,9 @@
         <v>0</v>
       </c>
       <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
         <v>0</v>
       </c>
     </row>
@@ -12828,37 +13132,37 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0.12935</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>0.00214</v>
       </c>
       <c r="F35">
-        <v>0.00213</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>0.00712</v>
       </c>
       <c r="H35">
-        <v>0.00721</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>0.00455</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>0.12821</v>
       </c>
       <c r="K35">
-        <v>0.11283</v>
+        <v>0</v>
       </c>
       <c r="L35">
-        <v>0.61548</v>
+        <v>0.1116</v>
       </c>
       <c r="M35">
-        <v>0.00791</v>
+        <v>0.7088100000000001</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>0.007860000000000001</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -12867,16 +13171,16 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>0.00201</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>0.00198</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
       <c r="T35">
-        <v>0.11059</v>
+        <v>0</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -12894,16 +13198,16 @@
         <v>0</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>0.02449</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.00481</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>0.00478</v>
       </c>
       <c r="AD35">
         <v>0</v>
@@ -12924,15 +13228,18 @@
         <v>0</v>
       </c>
       <c r="AJ35">
-        <v>0.00312</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>0.00301</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
         <v>0</v>
       </c>
     </row>
@@ -12948,40 +13255,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.00317</v>
+        <v>0.00324</v>
       </c>
       <c r="D36">
-        <v>0.01857</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>0.05593</v>
       </c>
       <c r="F36">
-        <v>0.05723</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="H36">
-        <v>0.02024</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>0.01895</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0.00151</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>0.35609</v>
+        <v>0.00154</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>0.35932</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -12990,10 +13297,10 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0.54319</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>0.54022</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -13056,6 +13363,9 @@
         <v>0</v>
       </c>
       <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
         <v>0</v>
       </c>
     </row>
@@ -13122,7 +13432,7 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>0.93119</v>
+        <v>0</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -13140,7 +13450,7 @@
         <v>0</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>0.9311</v>
       </c>
       <c r="AA37">
         <v>0</v>
@@ -13176,9 +13486,12 @@
         <v>0</v>
       </c>
       <c r="AL37">
-        <v>0.06881</v>
+        <v>0</v>
       </c>
       <c r="AM37">
+        <v>0.0689</v>
+      </c>
+      <c r="AN37">
         <v>0</v>
       </c>
     </row>
@@ -13197,37 +13510,37 @@
         <v>0.00036</v>
       </c>
       <c r="D38">
-        <v>0.72558</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>0.00027</v>
       </c>
       <c r="F38">
-        <v>0.00032</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>0.0442</v>
       </c>
       <c r="H38">
-        <v>0.04433</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>0.07457</v>
+        <v>0.07368</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>0.70707</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0.01635</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>0.00709</v>
+        <v>0.02456</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>0.00792</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -13236,16 +13549,16 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>0.00792</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>0.03914</v>
+        <v>0.008030000000000001</v>
       </c>
       <c r="S38">
-        <v>0.00542</v>
+        <v>0.03985</v>
       </c>
       <c r="T38">
-        <v>0.01789</v>
+        <v>0.0055</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -13263,16 +13576,16 @@
         <v>0</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>0.01853</v>
       </c>
       <c r="AA38">
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>0.05679</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>0.06574000000000001</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -13284,10 +13597,10 @@
         <v>0</v>
       </c>
       <c r="AG38">
-        <v>0.00423</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>0.00429</v>
       </c>
       <c r="AI38">
         <v>0</v>
@@ -13302,6 +13615,9 @@
         <v>0</v>
       </c>
       <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
         <v>0</v>
       </c>
     </row>
@@ -13320,56 +13636,56 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0.55116</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>0.0265</v>
       </c>
       <c r="F39">
-        <v>0.02651</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>0.01976</v>
       </c>
       <c r="H39">
-        <v>0.01209</v>
+        <v>0</v>
       </c>
       <c r="I39">
         <v>0.00651</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>0.54905</v>
       </c>
       <c r="K39">
-        <v>0.02605</v>
+        <v>0</v>
       </c>
       <c r="L39">
-        <v>0.16907</v>
+        <v>0.02603</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>0.25755</v>
       </c>
       <c r="N39">
         <v>0</v>
       </c>
       <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
         <v>0.01</v>
       </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
       <c r="Q39">
-        <v>0.02279</v>
+        <v>0</v>
       </c>
       <c r="R39">
+        <v>0.02278</v>
+      </c>
+      <c r="S39">
         <v>0.00465</v>
       </c>
-      <c r="S39">
+      <c r="T39">
         <v>0.00442</v>
       </c>
-      <c r="T39">
-        <v>0.09791</v>
-      </c>
       <c r="U39">
         <v>0</v>
       </c>
@@ -13392,10 +13708,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0.02651</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>0.03045</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -13407,10 +13723,10 @@
         <v>0</v>
       </c>
       <c r="AG39">
-        <v>0.04233</v>
+        <v>0</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>0.04231</v>
       </c>
       <c r="AI39">
         <v>0</v>
@@ -13425,6 +13741,9 @@
         <v>0</v>
       </c>
       <c r="AM39">
+        <v>0</v>
+      </c>
+      <c r="AN39">
         <v>0</v>
       </c>
     </row>
@@ -13443,25 +13762,25 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0.00155</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>0.97687</v>
       </c>
       <c r="F40">
-        <v>0.98053</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H40">
-        <v>0.00099</v>
+        <v>0</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>0.00156</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -13470,10 +13789,10 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0.01694</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>0.02057</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -13548,6 +13867,9 @@
         <v>0</v>
       </c>
       <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40">
         <v>0</v>
       </c>
     </row>
@@ -13566,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0.09153</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -13575,37 +13897,37 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>0.27369</v>
       </c>
       <c r="H41">
-        <v>0.27639</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>0.2665</v>
+        <v>0.26916</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>0.09107</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0.00074</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>0.00221</v>
+        <v>0.00077</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>0.00219</v>
       </c>
       <c r="O41">
-        <v>0.00066</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>0.00038</v>
+        <v>0.00067</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>0.00039</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -13614,7 +13936,7 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>0.1679</v>
+        <v>0</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -13632,19 +13954,19 @@
         <v>0</v>
       </c>
       <c r="Z41">
-        <v>0.14223</v>
+        <v>0.16904</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>0.14227</v>
       </c>
       <c r="AB41">
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>0.01778</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>0.01705</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -13653,13 +13975,13 @@
         <v>0</v>
       </c>
       <c r="AG41">
-        <v>0.009259999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH41">
-        <v>0.02442</v>
+        <v>0.00923</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>0.02448</v>
       </c>
       <c r="AJ41">
         <v>0</v>
@@ -13671,6 +13993,9 @@
         <v>0</v>
       </c>
       <c r="AM41">
+        <v>0</v>
+      </c>
+      <c r="AN41">
         <v>0</v>
       </c>
     </row>
@@ -13689,34 +14014,34 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0.14818</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>0.007979999999999999</v>
       </c>
       <c r="F42">
-        <v>0.00792</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>0.5791500000000001</v>
       </c>
       <c r="H42">
-        <v>0.5807600000000001</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>0.07954</v>
+        <v>0.07876</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>0.14922</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0.00114</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>0.10608</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -13725,19 +14050,19 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>0.0023</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>0.00232</v>
       </c>
       <c r="R42">
         <v>0</v>
       </c>
       <c r="S42">
-        <v>0.00359</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>0.10946</v>
+        <v>0.00354</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -13755,16 +14080,16 @@
         <v>0</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>0.00524</v>
       </c>
       <c r="AA42">
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>0.06408</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>0.06458999999999999</v>
       </c>
       <c r="AD42">
         <v>0</v>
@@ -13776,10 +14101,10 @@
         <v>0</v>
       </c>
       <c r="AG42">
-        <v>0.00304</v>
+        <v>0</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>0.00312</v>
       </c>
       <c r="AI42">
         <v>0</v>
@@ -13794,6 +14119,9 @@
         <v>0</v>
       </c>
       <c r="AM42">
+        <v>0</v>
+      </c>
+      <c r="AN42">
         <v>0</v>
       </c>
     </row>
@@ -13812,55 +14140,55 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0.01192</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>0.02752</v>
       </c>
       <c r="F43">
-        <v>0.02769</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>0.00661</v>
       </c>
       <c r="H43">
-        <v>0.00654</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>0.10587</v>
+        <v>0.10598</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>0.01195</v>
       </c>
       <c r="K43">
-        <v>0.03189</v>
+        <v>0</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>0.03198</v>
       </c>
       <c r="M43">
-        <v>0.22971</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>0.42026</v>
+        <v>0.23234</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>0.41052</v>
       </c>
       <c r="P43">
-        <v>0.04239</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>0.03863</v>
+        <v>0.04251</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>0.03688</v>
       </c>
       <c r="S43">
-        <v>0.00542</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>0.0001</v>
+        <v>0.00549</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -13893,10 +14221,10 @@
         <v>0</v>
       </c>
       <c r="AE43">
-        <v>0.07623000000000001</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>0.0765</v>
       </c>
       <c r="AG43">
         <v>0</v>
@@ -13911,12 +14239,15 @@
         <v>0</v>
       </c>
       <c r="AK43">
-        <v>0.00137</v>
+        <v>0</v>
       </c>
       <c r="AL43">
-        <v>0.002</v>
+        <v>0.0097</v>
       </c>
       <c r="AM43">
+        <v>0.00201</v>
+      </c>
+      <c r="AN43">
         <v>0</v>
       </c>
     </row>
@@ -13938,34 +14269,34 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>0.55996</v>
       </c>
       <c r="F44">
-        <v>0.5555600000000001</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>0.11008</v>
       </c>
       <c r="H44">
-        <v>0.10924</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0.00471</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>0.14208</v>
+        <v>0.00475</v>
       </c>
       <c r="L44">
-        <v>0.08457000000000001</v>
+        <v>0.14331</v>
       </c>
       <c r="M44">
-        <v>0.03698</v>
+        <v>0.08760999999999999</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>0.02693</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -13983,7 +14314,7 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>0.02354</v>
+        <v>0</v>
       </c>
       <c r="U44">
         <v>0</v>
@@ -14001,16 +14332,16 @@
         <v>0</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>0.02367</v>
       </c>
       <c r="AA44">
         <v>0</v>
       </c>
       <c r="AB44">
-        <v>0.04333</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>0.04369</v>
       </c>
       <c r="AD44">
         <v>0</v>
@@ -14040,6 +14371,9 @@
         <v>0</v>
       </c>
       <c r="AM44">
+        <v>0</v>
+      </c>
+      <c r="AN44">
         <v>0</v>
       </c>
     </row>
@@ -14061,10 +14395,10 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>0.01741</v>
       </c>
       <c r="F45">
-        <v>0.01869</v>
+        <v>0</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -14073,7 +14407,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>0.2013</v>
+        <v>0.19692</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -14085,31 +14419,31 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>0.21147</v>
+        <v>0</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>0.2132</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>0.19009</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>0.17502</v>
+        <v>0.18804</v>
       </c>
       <c r="R45">
-        <v>0.17963</v>
+        <v>0.17371</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>0.18368</v>
       </c>
       <c r="T45">
         <v>0</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>0.00083</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -14124,7 +14458,7 @@
         <v>0</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>0.00623</v>
       </c>
       <c r="AA45">
         <v>0</v>
@@ -14139,10 +14473,10 @@
         <v>0</v>
       </c>
       <c r="AE45">
-        <v>0.01646</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>0.01015</v>
       </c>
       <c r="AG45">
         <v>0</v>
@@ -14154,15 +14488,18 @@
         <v>0</v>
       </c>
       <c r="AJ45">
-        <v>0.00736</v>
+        <v>0</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>0.00983</v>
       </c>
       <c r="AL45">
         <v>0</v>
       </c>
       <c r="AM45">
+        <v>0</v>
+      </c>
+      <c r="AN45">
         <v>0</v>
       </c>
     </row>
@@ -14181,55 +14518,55 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0.15864</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>0.24904</v>
       </c>
       <c r="F46">
-        <v>0.25139</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>0.00236</v>
       </c>
       <c r="H46">
-        <v>0.00234</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>0.04682</v>
+        <v>0.0467</v>
       </c>
       <c r="J46">
-        <v>0.00156</v>
+        <v>0.15993</v>
       </c>
       <c r="K46">
-        <v>0.00292</v>
+        <v>0.00157</v>
       </c>
       <c r="L46">
-        <v>0.00431</v>
+        <v>0.00295</v>
       </c>
       <c r="M46">
-        <v>0.44658</v>
+        <v>0.01209</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>0.44723</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>0.00052</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0.00132</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>0.04365</v>
+        <v>0.00133</v>
       </c>
       <c r="S46">
-        <v>0.01133</v>
+        <v>0.04368</v>
       </c>
       <c r="T46">
-        <v>0.01226</v>
+        <v>0.01122</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -14247,16 +14584,16 @@
         <v>0</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>0.00232</v>
       </c>
       <c r="AA46">
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>0.00745</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>0.00899</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -14271,21 +14608,24 @@
         <v>0</v>
       </c>
       <c r="AH46">
-        <v>0.00154</v>
+        <v>0</v>
       </c>
       <c r="AI46">
-        <v>0</v>
+        <v>0.00155</v>
       </c>
       <c r="AJ46">
-        <v>0.007889999999999999</v>
+        <v>0</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>0.00791</v>
       </c>
       <c r="AL46">
-        <v>0</v>
+        <v>0.00059</v>
       </c>
       <c r="AM46">
+        <v>0</v>
+      </c>
+      <c r="AN46">
         <v>0</v>
       </c>
     </row>
@@ -14307,10 +14647,10 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>0.00046</v>
       </c>
       <c r="F47">
-        <v>0.00046</v>
+        <v>0</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -14319,7 +14659,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0.15785</v>
+        <v>0.15799</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -14331,28 +14671,28 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>0.08283</v>
+        <v>0</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>0.08291</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>0.0359</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>0.16015</v>
+        <v>0.03593</v>
       </c>
       <c r="R47">
-        <v>0.01749</v>
+        <v>0.15983</v>
       </c>
       <c r="S47">
-        <v>0.07179000000000001</v>
+        <v>0.0175</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -14373,10 +14713,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0.47354</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>0.47398</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -14409,6 +14749,9 @@
         <v>0</v>
       </c>
       <c r="AM47">
+        <v>0</v>
+      </c>
+      <c r="AN47">
         <v>0</v>
       </c>
     </row>
@@ -14430,16 +14773,16 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>0.03783</v>
       </c>
       <c r="F48">
-        <v>0.03811</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>0.02283</v>
       </c>
       <c r="H48">
-        <v>0.0228</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -14448,16 +14791,16 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0.18827</v>
+        <v>0</v>
       </c>
       <c r="L48">
-        <v>0.15147</v>
+        <v>0.18852</v>
       </c>
       <c r="M48">
-        <v>0.44137</v>
+        <v>0.15166</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>0.44097</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -14472,10 +14815,10 @@
         <v>0</v>
       </c>
       <c r="S48">
-        <v>0.10782</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>0.10796</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -14523,16 +14866,19 @@
         <v>0</v>
       </c>
       <c r="AJ48">
-        <v>0.03257</v>
+        <v>0</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>0.03262</v>
       </c>
       <c r="AL48">
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>0.01759</v>
+        <v>0</v>
+      </c>
+      <c r="AN48">
+        <v>0.01761</v>
       </c>
     </row>
     <row r="49">
@@ -14550,55 +14896,55 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0.0077</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>0.02795</v>
       </c>
       <c r="F49">
-        <v>0.02789</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>0.10153</v>
       </c>
       <c r="H49">
-        <v>0.10246</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>0.03009</v>
+        <v>0.02461</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>0.00766</v>
       </c>
       <c r="K49">
-        <v>0.32866</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>0.23097</v>
+        <v>0.33014</v>
       </c>
       <c r="M49">
-        <v>0.08141</v>
+        <v>0.27231</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>0.08116</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>0.00369</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>0.00367</v>
       </c>
       <c r="R49">
         <v>0</v>
       </c>
       <c r="S49">
-        <v>0.1123</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>0.0723</v>
+        <v>0.11126</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -14616,25 +14962,25 @@
         <v>0</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>0.03757</v>
       </c>
       <c r="AA49">
         <v>0</v>
       </c>
       <c r="AB49">
-        <v>0.00083</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>0.00044</v>
       </c>
       <c r="AD49">
         <v>0</v>
       </c>
       <c r="AE49">
-        <v>0.0017</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>0.00171</v>
       </c>
       <c r="AG49">
         <v>0</v>
@@ -14655,6 +15001,9 @@
         <v>0</v>
       </c>
       <c r="AM49">
+        <v>0</v>
+      </c>
+      <c r="AN49">
         <v>0</v>
       </c>
     </row>
@@ -14676,10 +15025,10 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>0.89152</v>
       </c>
       <c r="F50">
-        <v>0.90038</v>
+        <v>0</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -14694,16 +15043,16 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0.009509999999999999</v>
+        <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>0.009520000000000001</v>
       </c>
       <c r="M50">
-        <v>0.09011</v>
+        <v>0</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>0.09896000000000001</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -14778,6 +15127,9 @@
         <v>0</v>
       </c>
       <c r="AM50">
+        <v>0</v>
+      </c>
+      <c r="AN50">
         <v>0</v>
       </c>
     </row>
@@ -14805,31 +15157,31 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>0.008070000000000001</v>
       </c>
       <c r="H51">
-        <v>0.00796</v>
+        <v>0</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0.13605</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>0.00658</v>
+        <v>0.1368</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>0.00667</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>0.00461</v>
       </c>
       <c r="N51">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>0.00305</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -14844,10 +15196,10 @@
         <v>0</v>
       </c>
       <c r="T51">
-        <v>0.00455</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>0.84187</v>
+        <v>0.8408099999999999</v>
       </c>
       <c r="V51">
         <v>0</v>
@@ -14901,6 +15253,9 @@
         <v>0</v>
       </c>
       <c r="AM51">
+        <v>0</v>
+      </c>
+      <c r="AN51">
         <v>0</v>
       </c>
     </row>
@@ -14922,10 +15277,10 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>0.00065</v>
       </c>
       <c r="F52">
-        <v>0.00065</v>
+        <v>0</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -14937,19 +15292,19 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0.78944</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>0.14963</v>
+        <v>0.78982</v>
       </c>
       <c r="L52">
-        <v>0.00877</v>
+        <v>0.14971</v>
       </c>
       <c r="M52">
-        <v>0.03038</v>
+        <v>0.00878</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>0.0304</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -14970,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>0.02112</v>
+        <v>0.02064</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -15024,6 +15379,9 @@
         <v>0</v>
       </c>
       <c r="AM52">
+        <v>0</v>
+      </c>
+      <c r="AN52">
         <v>0</v>
       </c>
     </row>
@@ -15039,7 +15397,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>0.0629</v>
+        <v>0.06322999999999999</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -15048,37 +15406,37 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>0.10749</v>
       </c>
       <c r="G53">
-        <v>0.10687</v>
+        <v>0.03756</v>
       </c>
       <c r="H53">
-        <v>0.03759</v>
+        <v>0</v>
       </c>
       <c r="I53">
         <v>0</v>
       </c>
       <c r="J53">
-        <v>0.01134</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>0.00356</v>
+        <v>0.01142</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>0.00359</v>
       </c>
       <c r="M53">
-        <v>0.00487</v>
+        <v>0</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>0.00491</v>
       </c>
       <c r="O53">
-        <v>0.01819</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>0.0184</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -15099,7 +15457,7 @@
         <v>0</v>
       </c>
       <c r="W53">
-        <v>0.62548</v>
+        <v>0.62429</v>
       </c>
       <c r="X53">
         <v>0</v>
@@ -15120,10 +15478,10 @@
         <v>0</v>
       </c>
       <c r="AD53">
-        <v>0.12918</v>
+        <v>0</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>0.12911</v>
       </c>
       <c r="AF53">
         <v>0</v>
@@ -15147,6 +15505,9 @@
         <v>0</v>
       </c>
       <c r="AM53">
+        <v>0</v>
+      </c>
+      <c r="AN53">
         <v>0</v>
       </c>
     </row>
@@ -15162,25 +15523,25 @@
         </is>
       </c>
       <c r="C54">
-        <v>0.1127</v>
+        <v>0.11346</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>0.12759</v>
       </c>
       <c r="F54">
-        <v>0.12793</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>0.10175</v>
       </c>
       <c r="H54">
-        <v>0.10162</v>
+        <v>0</v>
       </c>
       <c r="I54">
-        <v>0.0083</v>
+        <v>0.00726</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -15189,16 +15550,16 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0.00475</v>
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>0.0042</v>
+        <v>0.00473</v>
       </c>
       <c r="N54">
-        <v>0.07290000000000001</v>
+        <v>0.00407</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>0.07201</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -15210,16 +15571,16 @@
         <v>0</v>
       </c>
       <c r="S54">
-        <v>0.00519</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>0.00415</v>
+        <v>0.00522</v>
       </c>
       <c r="U54">
         <v>0</v>
       </c>
       <c r="V54">
-        <v>0.54745</v>
+        <v>0.54373</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -15231,7 +15592,7 @@
         <v>0</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>0.00412</v>
       </c>
       <c r="AA54">
         <v>0</v>
@@ -15264,12 +15625,15 @@
         <v>0</v>
       </c>
       <c r="AK54">
-        <v>0.01081</v>
+        <v>0</v>
       </c>
       <c r="AL54">
-        <v>0</v>
+        <v>0.01605</v>
       </c>
       <c r="AM54">
+        <v>0</v>
+      </c>
+      <c r="AN54">
         <v>0</v>
       </c>
     </row>
@@ -15285,22 +15649,22 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.02077</v>
+        <v>0.02084</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0.01641</v>
+        <v>0</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>0.01916</v>
       </c>
       <c r="H55">
-        <v>0.0191</v>
+        <v>0.0165</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -15309,16 +15673,16 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0.74308</v>
+        <v>0</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>0.74035</v>
       </c>
       <c r="M55">
-        <v>0.1913</v>
+        <v>0.00915</v>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -15336,7 +15700,7 @@
         <v>0</v>
       </c>
       <c r="T55">
-        <v>0.00933</v>
+        <v>0</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -15393,6 +15757,9 @@
         <v>0</v>
       </c>
       <c r="AM55">
+        <v>0</v>
+      </c>
+      <c r="AN55">
         <v>0</v>
       </c>
     </row>
@@ -15426,7 +15793,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>0.94291</v>
+        <v>0.94294</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -15447,14 +15814,14 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>0.05546</v>
+        <v>0</v>
       </c>
       <c r="Q56">
+        <v>0.05543</v>
+      </c>
+      <c r="R56">
         <v>0.00162</v>
       </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
       <c r="S56">
         <v>0</v>
       </c>
@@ -15516,6 +15883,9 @@
         <v>0</v>
       </c>
       <c r="AM56">
+        <v>0</v>
+      </c>
+      <c r="AN56">
         <v>0</v>
       </c>
     </row>
@@ -15531,7 +15901,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>0.20632</v>
+        <v>0.19942</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -15549,7 +15919,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>0.76625</v>
+        <v>0.77399</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -15579,10 +15949,10 @@
         <v>0</v>
       </c>
       <c r="S57">
-        <v>0.02743</v>
+        <v>0</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>0.02659</v>
       </c>
       <c r="U57">
         <v>0</v>
@@ -15639,6 +16009,9 @@
         <v>0</v>
       </c>
       <c r="AM57">
+        <v>0</v>
+      </c>
+      <c r="AN57">
         <v>0</v>
       </c>
     </row>
@@ -15672,7 +16045,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>0.02377</v>
+        <v>0.02343</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -15693,10 +16066,10 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>0.7706499999999999</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>0.77394</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -15750,10 +16123,10 @@
         <v>0</v>
       </c>
       <c r="AI58">
-        <v>0.20559</v>
+        <v>0</v>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>0.20264</v>
       </c>
       <c r="AK58">
         <v>0</v>
@@ -15762,6 +16135,9 @@
         <v>0</v>
       </c>
       <c r="AM58">
+        <v>0</v>
+      </c>
+      <c r="AN58">
         <v>0</v>
       </c>
     </row>
@@ -15777,10 +16153,10 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.03588</v>
+        <v>0.03581</v>
       </c>
       <c r="D59">
-        <v>0.00631</v>
+        <v>0</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -15795,10 +16171,10 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>0.0027</v>
+        <v>0.00265</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>0.00608</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -15810,16 +16186,16 @@
         <v>0</v>
       </c>
       <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
         <v>0.00156</v>
       </c>
-      <c r="O59">
-        <v>0.32029</v>
-      </c>
       <c r="P59">
-        <v>0.00505</v>
+        <v>0.32069</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -15840,7 +16216,7 @@
         <v>0</v>
       </c>
       <c r="X59">
-        <v>0.58835</v>
+        <v>0.5841499999999999</v>
       </c>
       <c r="Y59">
         <v>0</v>
@@ -15855,10 +16231,10 @@
         <v>0</v>
       </c>
       <c r="AC59">
-        <v>0.03973</v>
+        <v>0</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>0.03979</v>
       </c>
       <c r="AE59">
         <v>0</v>
@@ -15879,12 +16255,15 @@
         <v>0</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>0.00415</v>
       </c>
       <c r="AL59">
         <v>0</v>
       </c>
       <c r="AM59">
+        <v>0</v>
+      </c>
+      <c r="AN59">
         <v>0</v>
       </c>
     </row>
@@ -15900,7 +16279,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.16426</v>
+        <v>0.16561</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -15921,25 +16300,25 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>0.83247</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>0.82052</v>
       </c>
       <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
         <v>0.0009700000000000001</v>
       </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
       <c r="N60">
         <v>0</v>
       </c>
       <c r="O60">
-        <v>0.0023</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>0.00231</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -15954,7 +16333,7 @@
         <v>0</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>0.01059</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -16008,6 +16387,9 @@
         <v>0</v>
       </c>
       <c r="AM60">
+        <v>0</v>
+      </c>
+      <c r="AN60">
         <v>0</v>
       </c>
     </row>
@@ -16023,40 +16405,40 @@
         </is>
       </c>
       <c r="C61">
-        <v>0.97505</v>
+        <v>0.97346</v>
       </c>
       <c r="D61">
-        <v>0.00031</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>0.00045</v>
       </c>
       <c r="F61">
-        <v>0.00045</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>0.00203</v>
       </c>
       <c r="H61">
-        <v>0.0021</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <v>0.00051</v>
       </c>
       <c r="J61">
-        <v>0.00123</v>
+        <v>0.0003</v>
       </c>
       <c r="K61">
-        <v>0.008410000000000001</v>
+        <v>0.00124</v>
       </c>
       <c r="L61">
-        <v>0.00565</v>
+        <v>0.008240000000000001</v>
       </c>
       <c r="M61">
-        <v>0.00249</v>
+        <v>0.00619</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>0.00246</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -16071,13 +16453,13 @@
         <v>0</v>
       </c>
       <c r="S61">
-        <v>0.00197</v>
+        <v>0</v>
       </c>
       <c r="T61">
-        <v>0.00121</v>
+        <v>0.00195</v>
       </c>
       <c r="U61">
-        <v>0.00023</v>
+        <v>0.00211</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -16092,7 +16474,7 @@
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>0.00099</v>
       </c>
       <c r="AA61">
         <v>0</v>
@@ -16110,7 +16492,7 @@
         <v>0</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>8.000000000000001E-05</v>
       </c>
       <c r="AG61">
         <v>0</v>
@@ -16125,12 +16507,15 @@
         <v>0</v>
       </c>
       <c r="AK61">
-        <v>0.00039</v>
+        <v>0</v>
       </c>
       <c r="AL61">
         <v>0</v>
       </c>
       <c r="AM61">
+        <v>0</v>
+      </c>
+      <c r="AN61">
         <v>0</v>
       </c>
     </row>
@@ -16146,7 +16531,7 @@
         </is>
       </c>
       <c r="C62">
-        <v>0.00624</v>
+        <v>0.00625</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -16173,10 +16558,10 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>0.99376</v>
+        <v>0</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>0.99375</v>
       </c>
       <c r="N62">
         <v>0</v>
@@ -16254,6 +16639,9 @@
         <v>0</v>
       </c>
       <c r="AM62">
+        <v>0</v>
+      </c>
+      <c r="AN62">
         <v>0</v>
       </c>
     </row>
@@ -16269,7 +16657,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>0.9944</v>
+        <v>0.99229</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -16293,10 +16681,10 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>0.0056</v>
+        <v>0</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>0.00559</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -16323,7 +16711,7 @@
         <v>0</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>0.00212</v>
       </c>
       <c r="V63">
         <v>0</v>
@@ -16377,6 +16765,9 @@
         <v>0</v>
       </c>
       <c r="AM63">
+        <v>0</v>
+      </c>
+      <c r="AN63">
         <v>0</v>
       </c>
     </row>
@@ -16392,10 +16783,10 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.20825</v>
+        <v>0.21132</v>
       </c>
       <c r="D64">
-        <v>0.51701</v>
+        <v>0</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -16404,25 +16795,25 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>0.02427</v>
       </c>
       <c r="H64">
-        <v>0.02393</v>
+        <v>0</v>
       </c>
       <c r="I64">
         <v>0</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>0.52445</v>
       </c>
       <c r="K64">
-        <v>0.00048</v>
+        <v>0</v>
       </c>
       <c r="L64">
-        <v>0.19574</v>
+        <v>0.00049</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>0.18412</v>
       </c>
       <c r="N64">
         <v>0</v>
@@ -16446,7 +16837,7 @@
         <v>0</v>
       </c>
       <c r="U64">
-        <v>0.00709</v>
+        <v>0.00719</v>
       </c>
       <c r="V64">
         <v>0</v>
@@ -16467,10 +16858,10 @@
         <v>0</v>
       </c>
       <c r="AB64">
-        <v>0.04749</v>
+        <v>0</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>0.04816</v>
       </c>
       <c r="AD64">
         <v>0</v>
@@ -16500,6 +16891,9 @@
         <v>0</v>
       </c>
       <c r="AM64">
+        <v>0</v>
+      </c>
+      <c r="AN64">
         <v>0</v>
       </c>
     </row>
@@ -16518,37 +16912,37 @@
         <v>0</v>
       </c>
       <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
         <v>0.04008</v>
       </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
       <c r="K65">
-        <v>0.88528</v>
+        <v>0</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>0.88515</v>
       </c>
       <c r="M65">
-        <v>0.03652</v>
+        <v>0</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>0.03666</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -16566,63 +16960,66 @@
         <v>0</v>
       </c>
       <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65">
+        <v>0</v>
+      </c>
+      <c r="AI65">
+        <v>0</v>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
         <v>0.03811</v>
       </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>0</v>
-      </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
-      </c>
-      <c r="AB65">
-        <v>0</v>
-      </c>
-      <c r="AC65">
-        <v>0</v>
-      </c>
-      <c r="AD65">
-        <v>0</v>
-      </c>
-      <c r="AE65">
-        <v>0</v>
-      </c>
-      <c r="AF65">
-        <v>0</v>
-      </c>
-      <c r="AG65">
-        <v>0</v>
-      </c>
-      <c r="AH65">
-        <v>0</v>
-      </c>
-      <c r="AI65">
-        <v>0</v>
-      </c>
-      <c r="AJ65">
-        <v>0</v>
-      </c>
-      <c r="AK65">
-        <v>0</v>
-      </c>
-      <c r="AL65">
-        <v>0</v>
-      </c>
       <c r="AM65">
+        <v>0</v>
+      </c>
+      <c r="AN65">
         <v>0</v>
       </c>
     </row>
@@ -16656,7 +17053,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>0.30172</v>
+        <v>0.29855</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -16668,10 +17065,10 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>0.31034</v>
+        <v>0</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>0.31304</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -16743,9 +17140,12 @@
         <v>0</v>
       </c>
       <c r="AL66">
-        <v>0.38793</v>
+        <v>0</v>
       </c>
       <c r="AM66">
+        <v>0.38841</v>
+      </c>
+      <c r="AN66">
         <v>0</v>
       </c>
     </row>
